--- a/data/excel/ebidta-calculation-cn-lounge.xlsx
+++ b/data/excel/ebidta-calculation-cn-lounge.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MatthiasLavenant\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B96F4BE-3915-47B8-98B8-171892EF7F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208B917E-2F1C-43AB-B341-D5AC45D0EC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C2EDA614-6673-4EA7-B53D-1FAD471EC239}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C2EDA614-6673-4EA7-B53D-1FAD471EC239}"/>
   </bookViews>
   <sheets>
     <sheet name="EBIDTA 2" sheetId="1" r:id="rId1"/>
@@ -1632,22 +1632,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1668,7 +1653,22 @@
     <xf numFmtId="2" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5691,11 +5691,11 @@
     </row>
     <row r="2" spans="2:175" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C2" s="2"/>
-      <c r="D2" s="83">
+      <c r="D2" s="78">
         <f>'[1]Overview 2026'!B24</f>
         <v>46025</v>
       </c>
-      <c r="E2" s="83"/>
+      <c r="E2" s="78"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2"/>
@@ -6047,11 +6047,11 @@
         <f>'[1]Overview 2026'!J3</f>
         <v>9</v>
       </c>
-      <c r="D4" s="84" t="str">
+      <c r="D4" s="79" t="str">
         <f>VLOOKUP(D$2,'[1]Overview 2026'!$B$7:$AC$52,$C4,FALSE)</f>
         <v>CLOONEE</v>
       </c>
-      <c r="E4" s="84"/>
+      <c r="E4" s="79"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4"/>
@@ -6231,11 +6231,11 @@
         <f>'[1]Overview 2026'!L3</f>
         <v>11</v>
       </c>
-      <c r="D5" s="85">
+      <c r="D5" s="80">
         <f>VLOOKUP(D$2,'[1]Overview 2026'!$B$7:$AC$52,$C5,FALSE)</f>
         <v>100000</v>
       </c>
-      <c r="E5" s="86"/>
+      <c r="E5" s="81"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5"/>
@@ -6412,11 +6412,11 @@
         <v>1</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="87">
+      <c r="D6" s="82">
         <f>IFERROR(D5/D8,"")</f>
         <v>0.45454545454545453</v>
       </c>
-      <c r="E6" s="88"/>
+      <c r="E6" s="83"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6"/>
@@ -6771,11 +6771,11 @@
         <f>'[1]Overview 2026'!F3</f>
         <v>5</v>
       </c>
-      <c r="D8" s="89">
+      <c r="D8" s="77">
         <f>D15+D16</f>
         <v>220000</v>
       </c>
-      <c r="E8" s="89"/>
+      <c r="E8" s="77"/>
     </row>
     <row r="9" spans="2:175" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
@@ -6785,22 +6785,22 @@
         <f>'[1]Overview 2026'!H3</f>
         <v>7</v>
       </c>
-      <c r="D9" s="89">
+      <c r="D9" s="77">
         <f>VLOOKUP(D$2,'[1]Overview 2026'!$B$7:$AC$52,$C9,FALSE)</f>
         <v>101500</v>
       </c>
-      <c r="E9" s="89"/>
+      <c r="E9" s="77"/>
     </row>
     <row r="10" spans="2:175" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="15"/>
-      <c r="D10" s="78">
+      <c r="D10" s="85">
         <f>SUM(D8:E9)</f>
         <v>321500</v>
       </c>
-      <c r="E10" s="78"/>
+      <c r="E10" s="85"/>
     </row>
     <row r="11" spans="2:175" x14ac:dyDescent="0.25">
       <c r="B11" s="16" t="s">
@@ -6810,11 +6810,11 @@
         <f>'[1]Overview 2026'!D3</f>
         <v>3</v>
       </c>
-      <c r="D11" s="79" t="str">
+      <c r="D11" s="86" t="str">
         <f>IF(VLOOKUP(D$2,'[1]Overview 2026'!$B6:$AC$52,$C11,FALSE)=0,"",VLOOKUP(D$2,'[1]Overview 2026'!$B6:$AC$52,$C11,FALSE))</f>
         <v/>
       </c>
-      <c r="E11" s="79"/>
+      <c r="E11" s="86"/>
     </row>
     <row r="12" spans="2:175" x14ac:dyDescent="0.25">
       <c r="B12" s="16" t="s">
@@ -6824,11 +6824,11 @@
         <f>'[1]Overview 2026'!C3</f>
         <v>2</v>
       </c>
-      <c r="D12" s="79" t="str">
+      <c r="D12" s="86" t="str">
         <f>IF(VLOOKUP(D$2,'[1]Overview 2026'!$B7:$AC$52,$C12,FALSE)=0,"",VLOOKUP(D$2,'[1]Overview 2026'!$B7:$AC$52,$C12,FALSE))</f>
         <v/>
       </c>
-      <c r="E12" s="79"/>
+      <c r="E12" s="86"/>
     </row>
     <row r="13" spans="2:175" x14ac:dyDescent="0.25">
       <c r="B13" s="18"/>
@@ -6891,11 +6891,11 @@
       <c r="B19" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="80">
+      <c r="D19" s="87">
         <f>E30</f>
         <v>28</v>
       </c>
-      <c r="E19" s="80"/>
+      <c r="E19" s="87"/>
       <c r="F19" s="29"/>
       <c r="G19" s="29"/>
     </row>
@@ -6903,11 +6903,11 @@
       <c r="B20" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="81">
+      <c r="D20" s="88">
         <f>D16/D19</f>
         <v>7142.8571428571431</v>
       </c>
-      <c r="E20" s="81"/>
+      <c r="E20" s="88"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="18"/>
@@ -6920,11 +6920,11 @@
         <f>'[1]Overview 2026'!R3</f>
         <v>17</v>
       </c>
-      <c r="D22" s="82" t="str">
+      <c r="D22" s="89" t="str">
         <f>IF(VLOOKUP(D$2,'[1]Overview 2026'!$B$7:$AC$52,$C22,FALSE)=0,"Beach Club",VLOOKUP(D$2,'[1]Overview 2026'!$B$7:$AC$52,$C22,FALSE))</f>
         <v>Beach Club</v>
       </c>
-      <c r="E22" s="82"/>
+      <c r="E22" s="89"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -7642,11 +7642,11 @@
       </c>
       <c r="D53" s="25">
         <f>'OPEX DATA 2'!U161</f>
-        <v>0.24153846153846154</v>
+        <v>0.13802197802197802</v>
       </c>
       <c r="E53" s="13">
         <f t="shared" ref="E53:E101" si="3">D53/D$36</f>
-        <v>7.5128603899988033E-7</v>
+        <v>4.2930630799993163E-7</v>
       </c>
     </row>
     <row r="54" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7656,11 +7656,11 @@
       </c>
       <c r="D54" s="25">
         <f>'OPEX DATA 2'!U162</f>
-        <v>315.81653846153847</v>
+        <v>180.4665934065934</v>
       </c>
       <c r="E54" s="13">
         <f t="shared" si="3"/>
-        <v>9.8232204809187715E-4</v>
+        <v>5.6132688462392968E-4</v>
       </c>
     </row>
     <row r="55" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7670,11 +7670,11 @@
       </c>
       <c r="D55" s="25">
         <f>'OPEX DATA 2'!U163</f>
-        <v>121.49442307692306</v>
+        <v>69.425384615384601</v>
       </c>
       <c r="E55" s="13">
         <f t="shared" si="3"/>
-        <v>3.7789867208996283E-4</v>
+        <v>2.1594209833712162E-4</v>
       </c>
     </row>
     <row r="56" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7684,11 +7684,11 @@
       </c>
       <c r="D56" s="25">
         <f>'OPEX DATA 2'!U164</f>
-        <v>38.287307692307692</v>
+        <v>21.87846153846154</v>
       </c>
       <c r="E56" s="13">
         <f t="shared" si="3"/>
-        <v>1.1908960401961957E-4</v>
+        <v>6.8051202296925471E-5</v>
       </c>
     </row>
     <row r="57" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7698,11 +7698,11 @@
       </c>
       <c r="D57" s="25">
         <f>'OPEX DATA 2'!U165</f>
-        <v>54.47538461538462</v>
+        <v>31.12879120879121</v>
       </c>
       <c r="E57" s="13">
         <f t="shared" si="3"/>
-        <v>1.6944132073214502E-4</v>
+        <v>9.6823611846939993E-5</v>
       </c>
     </row>
     <row r="58" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7712,11 +7712,11 @@
       </c>
       <c r="D58" s="25">
         <f>'OPEX DATA 2'!U166</f>
-        <v>174.56384615384616</v>
+        <v>99.750769230769237</v>
       </c>
       <c r="E58" s="13">
         <f t="shared" si="3"/>
-        <v>5.4296686206484028E-4</v>
+        <v>3.102667783227659E-4</v>
       </c>
     </row>
     <row r="59" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7726,11 +7726,11 @@
       </c>
       <c r="D59" s="25">
         <f>'OPEX DATA 2'!U167</f>
-        <v>147.65269230769232</v>
+        <v>84.37296703296704</v>
       </c>
       <c r="E59" s="13">
         <f t="shared" si="3"/>
-        <v>4.5926187342983614E-4</v>
+        <v>2.6243535624562067E-4</v>
       </c>
     </row>
     <row r="60" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7740,11 +7740,11 @@
       </c>
       <c r="D60" s="25">
         <f>'OPEX DATA 2'!U168</f>
-        <v>251.86307692307693</v>
+        <v>143.92175824175825</v>
       </c>
       <c r="E60" s="13">
         <f t="shared" si="3"/>
-        <v>7.8339992822107915E-4</v>
+        <v>4.4765710184061668E-4</v>
       </c>
     </row>
     <row r="61" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7754,11 +7754,11 @@
       </c>
       <c r="D61" s="25">
         <f>'OPEX DATA 2'!U169</f>
-        <v>22.196346153846154</v>
+        <v>12.683626373626373</v>
       </c>
       <c r="E61" s="13">
         <f t="shared" si="3"/>
-        <v>6.9039956932647449E-5</v>
+        <v>3.9451403961512826E-5</v>
       </c>
     </row>
     <row r="62" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7768,11 +7768,11 @@
       </c>
       <c r="D62" s="25">
         <f>'OPEX DATA 2'!U170</f>
-        <v>375.3194230769231</v>
+        <v>214.46824175824176</v>
       </c>
       <c r="E62" s="13">
         <f t="shared" si="3"/>
-        <v>1.1674010049048931E-3</v>
+        <v>6.6708628851708165E-4</v>
       </c>
     </row>
     <row r="63" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7782,11 +7782,11 @@
       </c>
       <c r="D63" s="25">
         <f>'OPEX DATA 2'!U171</f>
-        <v>195.05365384615385</v>
+        <v>111.45923076923077</v>
       </c>
       <c r="E63" s="13">
         <f t="shared" si="3"/>
-        <v>6.0669876779519084E-4</v>
+        <v>3.4668501016868046E-4</v>
       </c>
     </row>
     <row r="64" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7838,11 +7838,11 @@
       </c>
       <c r="D67" s="25">
         <f>'OPEX DATA 2'!U175</f>
-        <v>159.91</v>
+        <v>91.377142857142857</v>
       </c>
       <c r="E67" s="13">
         <f t="shared" si="3"/>
-        <v>4.9738724727838252E-4</v>
+        <v>2.8422128415907575E-4</v>
       </c>
     </row>
     <row r="68" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7852,11 +7852,11 @@
       </c>
       <c r="D68" s="25">
         <f>'OPEX DATA 2'!U176</f>
-        <v>284.53557692307692</v>
+        <v>162.59175824175824</v>
       </c>
       <c r="E68" s="13">
         <f t="shared" si="3"/>
-        <v>8.8502512262232322E-4</v>
+        <v>5.0572864149847044E-4</v>
       </c>
     </row>
     <row r="69" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7866,11 +7866,11 @@
       </c>
       <c r="D69" s="25">
         <f>'OPEX DATA 2'!U177</f>
-        <v>199.30980769230771</v>
+        <v>113.89131868131869</v>
       </c>
       <c r="E69" s="13">
         <f t="shared" si="3"/>
-        <v>6.1993719344419196E-4</v>
+        <v>3.5424982482525254E-4</v>
       </c>
     </row>
     <row r="70" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7880,11 +7880,11 @@
       </c>
       <c r="D70" s="25">
         <f>'OPEX DATA 2'!U178</f>
-        <v>15.196153846153846</v>
+        <v>8.6835164835164829</v>
       </c>
       <c r="E70" s="13">
         <f t="shared" si="3"/>
-        <v>4.7266419428161261E-5</v>
+        <v>2.7009382530377862E-5</v>
       </c>
     </row>
     <row r="71" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7894,11 +7894,11 @@
       </c>
       <c r="D71" s="25">
         <f>'OPEX DATA 2'!U179</f>
-        <v>164.88173076923078</v>
+        <v>94.218131868131877</v>
       </c>
       <c r="E71" s="13">
         <f t="shared" si="3"/>
-        <v>5.1285141763368831E-4</v>
+        <v>2.9305795293353617E-4</v>
       </c>
     </row>
     <row r="72" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7908,11 +7908,11 @@
       </c>
       <c r="D72" s="25">
         <f>'OPEX DATA 2'!U180</f>
-        <v>358.49807692307695</v>
+        <v>204.85604395604398</v>
       </c>
       <c r="E72" s="13">
         <f t="shared" si="3"/>
-        <v>1.1150795549706904E-3</v>
+        <v>6.3718831712610881E-4</v>
       </c>
     </row>
     <row r="73" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7936,11 +7936,11 @@
       </c>
       <c r="D74" s="25">
         <f>'OPEX DATA 2'!U182</f>
-        <v>11.730961538461539</v>
+        <v>6.7034065934065934</v>
       </c>
       <c r="E74" s="13">
         <f t="shared" si="3"/>
-        <v>3.6488216293815053E-5</v>
+        <v>2.0850409310751456E-5</v>
       </c>
     </row>
     <row r="75" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7950,11 +7950,11 @@
       </c>
       <c r="D75" s="25">
         <f>'OPEX DATA 2'!U183</f>
-        <v>131.67096153846154</v>
+        <v>75.240549450549452</v>
       </c>
       <c r="E75" s="13">
         <f t="shared" si="3"/>
-        <v>4.0955197990190216E-4</v>
+        <v>2.3402970280108693E-4</v>
       </c>
     </row>
     <row r="76" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7964,11 +7964,11 @@
       </c>
       <c r="D76" s="25">
         <f>'OPEX DATA 2'!U184</f>
-        <v>21.372692307692304</v>
+        <v>12.212967032967031</v>
       </c>
       <c r="E76" s="13">
         <f t="shared" si="3"/>
-        <v>6.6478047613350867E-5</v>
+        <v>3.7987455779057637E-5</v>
       </c>
     </row>
     <row r="77" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7978,11 +7978,11 @@
       </c>
       <c r="D77" s="25">
         <f>'OPEX DATA 2'!U185</f>
-        <v>39.365384615384613</v>
+        <v>22.494505494505493</v>
       </c>
       <c r="E77" s="13">
         <f t="shared" si="3"/>
-        <v>1.2244287594209832E-4</v>
+        <v>6.9967357681199047E-5</v>
       </c>
     </row>
     <row r="78" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8006,11 +8006,11 @@
       </c>
       <c r="D79" s="25">
         <f>'OPEX DATA 2'!U187</f>
-        <v>41.405192307692303</v>
+        <v>23.660109890109887</v>
       </c>
       <c r="E79" s="13">
         <f t="shared" si="3"/>
-        <v>1.2878753439406627E-4</v>
+        <v>7.3592876796609285E-5</v>
       </c>
     </row>
     <row r="80" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8020,11 +8020,11 @@
       </c>
       <c r="D80" s="25">
         <f>'OPEX DATA 2'!U188</f>
-        <v>97.980576923076924</v>
+        <v>55.988901098901103</v>
       </c>
       <c r="E80" s="13">
         <f t="shared" si="3"/>
-        <v>3.0476073693025483E-4</v>
+        <v>1.7414899253157418E-4</v>
       </c>
     </row>
     <row r="81" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8034,11 +8034,11 @@
       </c>
       <c r="D81" s="25">
         <f>'OPEX DATA 2'!U189</f>
-        <v>483.09269230769229</v>
+        <v>276.05296703296705</v>
       </c>
       <c r="E81" s="13">
         <f t="shared" si="3"/>
-        <v>1.5026211269290584E-3</v>
+        <v>8.5864064395946207E-4</v>
       </c>
     </row>
     <row r="82" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8076,11 +8076,11 @@
       </c>
       <c r="D84" s="25">
         <f>'OPEX DATA 2'!U192</f>
-        <v>93.671346153846144</v>
+        <v>53.526483516483509</v>
       </c>
       <c r="E84" s="13">
         <f t="shared" si="3"/>
-        <v>2.9135721976312952E-4</v>
+        <v>1.6648983986464544E-4</v>
       </c>
     </row>
     <row r="85" spans="2:175" x14ac:dyDescent="0.25">
@@ -8091,11 +8091,11 @@
       <c r="C85" s="15"/>
       <c r="D85" s="33">
         <f>'OPEX DATA 2'!U193</f>
-        <v>732.3682692307691</v>
+        <v>418.49615384615379</v>
       </c>
       <c r="E85" s="34">
         <f t="shared" si="3"/>
-        <v>2.2779728436415833E-3</v>
+        <v>1.3016987677951907E-3</v>
       </c>
     </row>
     <row r="86" spans="2:175" x14ac:dyDescent="0.25">
@@ -8105,11 +8105,11 @@
       </c>
       <c r="D86" s="25">
         <f>'OPEX DATA 2'!U194</f>
-        <v>436.39134615384614</v>
+        <v>249.3664835164835</v>
       </c>
       <c r="E86" s="13">
         <f t="shared" si="3"/>
-        <v>1.3573603301830362E-3</v>
+        <v>7.7563447439030642E-4</v>
       </c>
     </row>
     <row r="87" spans="2:175" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8120,11 +8120,11 @@
       <c r="C87" s="2"/>
       <c r="D87" s="19">
         <f>'OPEX DATA 2'!U195</f>
-        <v>87.905576923076922</v>
+        <v>50.231758241758243</v>
       </c>
       <c r="E87" s="12">
         <f t="shared" si="3"/>
-        <v>2.734232563703792E-4</v>
+        <v>1.5624186078307386E-4</v>
       </c>
       <c r="F87" s="12"/>
       <c r="G87" s="12"/>
@@ -8318,11 +8318,11 @@
       </c>
       <c r="D89" s="25">
         <f>'OPEX DATA 2'!U197</f>
-        <v>30.485192307692309</v>
+        <v>17.420109890109892</v>
       </c>
       <c r="E89" s="13">
         <f t="shared" si="3"/>
-        <v>9.4821749013039843E-5</v>
+        <v>5.4183856578879915E-5</v>
       </c>
     </row>
     <row r="90" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8374,11 +8374,11 @@
       </c>
       <c r="D93" s="25">
         <f>'OPEX DATA 2'!U201</f>
-        <v>37.785576923076924</v>
+        <v>21.591758241758242</v>
       </c>
       <c r="E93" s="13">
         <f t="shared" si="3"/>
-        <v>1.1752901064720661E-4</v>
+        <v>6.7159434655546634E-5</v>
       </c>
     </row>
     <row r="94" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8487,11 +8487,11 @@
       <c r="C101" s="36"/>
       <c r="D101" s="37">
         <f>SUM(D53:D100)</f>
-        <v>105124.52134615385</v>
+        <v>102928.29791208792</v>
       </c>
       <c r="E101" s="38">
         <f t="shared" si="3"/>
-        <v>0.32698140387606173</v>
+        <v>0.32015022678720967</v>
       </c>
       <c r="F101" s="38"/>
       <c r="G101" s="38"/>
@@ -8527,11 +8527,11 @@
       </c>
       <c r="D105" s="25">
         <f>'OPEX DATA 2'!U216</f>
-        <v>136.86538461538458</v>
+        <v>78.208791208791197</v>
       </c>
       <c r="E105" s="13">
         <f t="shared" ref="E105:E130" si="4">D105/D$36</f>
-        <v>4.2570881684412002E-4</v>
+        <v>2.4326218105378289E-4</v>
       </c>
     </row>
     <row r="106" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8541,11 +8541,11 @@
       </c>
       <c r="D106" s="25">
         <f>'OPEX DATA 2'!U217</f>
-        <v>566.11923076923085</v>
+        <v>323.49670329670334</v>
       </c>
       <c r="E106" s="13">
         <f t="shared" si="4"/>
-        <v>1.7608685249431754E-3</v>
+        <v>1.0062105856818145E-3</v>
       </c>
     </row>
     <row r="107" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8555,11 +8555,11 @@
       </c>
       <c r="D107" s="25">
         <f>'OPEX DATA 2'!U218</f>
-        <v>56.692307692307693</v>
+        <v>32.395604395604394</v>
       </c>
       <c r="E107" s="13">
         <f t="shared" si="4"/>
-        <v>1.7633688240220122E-4</v>
+        <v>1.0076393280125784E-4</v>
       </c>
     </row>
     <row r="108" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8569,11 +8569,11 @@
       </c>
       <c r="D108" s="25">
         <f>'OPEX DATA 2'!U219</f>
-        <v>859.60500000000002</v>
+        <v>491.20285714285717</v>
       </c>
       <c r="E108" s="13">
         <f t="shared" si="4"/>
-        <v>2.6737325038880249E-3</v>
+        <v>1.5278471450788714E-3</v>
       </c>
     </row>
     <row r="109" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8583,11 +8583,11 @@
       </c>
       <c r="D109" s="25">
         <f>'OPEX DATA 2'!U220</f>
-        <v>33.871153846153845</v>
+        <v>19.354945054945055</v>
       </c>
       <c r="E109" s="13">
         <f t="shared" si="4"/>
-        <v>1.0535351118554851E-4</v>
+        <v>6.0202006391742005E-5</v>
       </c>
     </row>
     <row r="110" spans="2:175" x14ac:dyDescent="0.25">
@@ -8598,11 +8598,11 @@
       <c r="C110" s="15"/>
       <c r="D110" s="33">
         <f>'OPEX DATA 2'!U221</f>
-        <v>160.44846153846154</v>
+        <v>91.684835164835164</v>
       </c>
       <c r="E110" s="34">
         <f t="shared" si="4"/>
-        <v>4.9906208876659888E-4</v>
+        <v>2.8517833643805648E-4</v>
       </c>
     </row>
     <row r="111" spans="2:175" x14ac:dyDescent="0.25">
@@ -8612,11 +8612,11 @@
       </c>
       <c r="D111" s="25">
         <f>'OPEX DATA 2'!U222</f>
-        <v>4.1528846153846155</v>
+        <v>2.3730769230769231</v>
       </c>
       <c r="E111" s="13">
         <f t="shared" si="4"/>
-        <v>1.2917214977868166E-5</v>
+        <v>7.3812657016389525E-6</v>
       </c>
     </row>
     <row r="112" spans="2:175" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8627,11 +8627,11 @@
       <c r="C112" s="2"/>
       <c r="D112" s="19">
         <f>'OPEX DATA 2'!U223</f>
-        <v>14.536153846153846</v>
+        <v>8.3063736263736256</v>
       </c>
       <c r="E112" s="12">
         <f t="shared" si="4"/>
-        <v>4.5213542289747581E-5</v>
+        <v>2.5836309879855755E-5</v>
       </c>
       <c r="F112" s="12"/>
       <c r="G112" s="12"/>
@@ -8811,11 +8811,11 @@
       </c>
       <c r="D113" s="25">
         <f>'OPEX DATA 2'!U224</f>
-        <v>7.2649999999999997</v>
+        <v>4.1514285714285712</v>
       </c>
       <c r="E113" s="13">
         <f t="shared" si="4"/>
-        <v>2.2597200622083979E-5</v>
+        <v>1.2912686069762275E-5</v>
       </c>
     </row>
     <row r="114" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8825,11 +8825,11 @@
       </c>
       <c r="D114" s="25">
         <f>'OPEX DATA 2'!U225</f>
-        <v>12.499423076923078</v>
+        <v>7.1425274725274734</v>
       </c>
       <c r="E114" s="13">
         <f t="shared" si="4"/>
-        <v>3.8878454360569449E-5</v>
+        <v>2.2216259634611115E-5</v>
       </c>
     </row>
     <row r="115" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8839,11 +8839,11 @@
       </c>
       <c r="D115" s="25">
         <f>'OPEX DATA 2'!U226</f>
-        <v>3.9086538461538463</v>
+        <v>2.2335164835164836</v>
       </c>
       <c r="E115" s="13">
         <f t="shared" si="4"/>
-        <v>1.2157554731427205E-5</v>
+        <v>6.9471741322441165E-6</v>
       </c>
     </row>
     <row r="116" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8853,11 +8853,11 @@
       </c>
       <c r="D116" s="25">
         <f>'OPEX DATA 2'!U227</f>
-        <v>53.207115384615385</v>
+        <v>30.404065934065933</v>
       </c>
       <c r="E116" s="13">
         <f t="shared" si="4"/>
-        <v>1.6549647086972125E-4</v>
+        <v>9.4569411925555009E-5</v>
       </c>
     </row>
     <row r="117" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8867,11 +8867,11 @@
       </c>
       <c r="D117" s="25">
         <f>'OPEX DATA 2'!U228</f>
-        <v>9.919423076923076</v>
+        <v>5.6682417582417575</v>
       </c>
       <c r="E117" s="13">
         <f t="shared" si="4"/>
-        <v>3.0853571001315943E-5</v>
+        <v>1.7630612000751968E-5</v>
       </c>
     </row>
     <row r="118" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8881,11 +8881,11 @@
       </c>
       <c r="D118" s="25">
         <f>'OPEX DATA 2'!U229</f>
-        <v>7.7307692307692308</v>
+        <v>4.4175824175824179</v>
       </c>
       <c r="E118" s="13">
         <f t="shared" si="4"/>
-        <v>2.4045938509391076E-5</v>
+        <v>1.3740536291080616E-5</v>
       </c>
     </row>
     <row r="119" spans="2:175" x14ac:dyDescent="0.25">
@@ -8896,11 +8896,11 @@
       <c r="C119" s="15"/>
       <c r="D119" s="33">
         <f>'OPEX DATA 2'!U230</f>
-        <v>89.742115384615389</v>
+        <v>51.28120879120879</v>
       </c>
       <c r="E119" s="34">
         <f t="shared" si="4"/>
-        <v>2.7913566216054554E-4</v>
+        <v>1.5950609266316887E-4</v>
       </c>
     </row>
     <row r="120" spans="2:175" x14ac:dyDescent="0.25">
@@ -9110,11 +9110,11 @@
       <c r="C122" s="15"/>
       <c r="D122" s="33">
         <f>'OPEX DATA 2'!U233</f>
-        <v>4.9667307692307689</v>
+        <v>2.8381318681318679</v>
       </c>
       <c r="E122" s="34">
         <f t="shared" si="4"/>
-        <v>1.5448618255772219E-5</v>
+        <v>8.8277818604412689E-6</v>
       </c>
     </row>
     <row r="123" spans="2:175" x14ac:dyDescent="0.25">
@@ -9124,11 +9124,11 @@
       </c>
       <c r="D123" s="25">
         <f>'OPEX DATA 2'!U234</f>
-        <v>3.4480769230769233</v>
+        <v>1.9703296703296704</v>
       </c>
       <c r="E123" s="13">
         <f t="shared" si="4"/>
-        <v>1.072496710132791E-5</v>
+        <v>6.1285526293302345E-6</v>
       </c>
     </row>
     <row r="124" spans="2:175" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9139,11 +9139,11 @@
       <c r="C124" s="2"/>
       <c r="D124" s="19">
         <f>'OPEX DATA 2'!U235</f>
-        <v>36.242115384615381</v>
+        <v>20.709780219780217</v>
       </c>
       <c r="E124" s="12">
         <f t="shared" si="4"/>
-        <v>1.1272819715276946E-4</v>
+        <v>6.4416112658725408E-5</v>
       </c>
       <c r="F124" s="12"/>
       <c r="G124" s="12"/>
@@ -9323,11 +9323,11 @@
       </c>
       <c r="D125" s="25">
         <f>'OPEX DATA 2'!U236</f>
-        <v>2153.2390384615383</v>
+        <v>1230.4223076923076</v>
       </c>
       <c r="E125" s="13">
         <f t="shared" si="4"/>
-        <v>6.6974775690872108E-3</v>
+        <v>3.8271300394784064E-3</v>
       </c>
     </row>
     <row r="126" spans="2:175" x14ac:dyDescent="0.25">
@@ -9338,11 +9338,11 @@
       <c r="C126" s="15"/>
       <c r="D126" s="33">
         <f>'OPEX DATA 2'!U237</f>
-        <v>242.78615384615387</v>
+        <v>138.73494505494506</v>
       </c>
       <c r="E126" s="34">
         <f t="shared" si="4"/>
-        <v>7.5516688599114735E-4</v>
+        <v>4.3152393485208415E-4</v>
       </c>
     </row>
     <row r="127" spans="2:175" x14ac:dyDescent="0.25">
@@ -9352,11 +9352,11 @@
       </c>
       <c r="D127" s="25">
         <f>'OPEX DATA 2'!U238</f>
-        <v>2.4792307692307691</v>
+        <v>1.4167032967032966</v>
       </c>
       <c r="E127" s="13">
         <f t="shared" si="4"/>
-        <v>7.7114487378873073E-6</v>
+        <v>4.4065421359356039E-6</v>
       </c>
     </row>
     <row r="128" spans="2:175" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9367,11 +9367,11 @@
       <c r="C128" s="2"/>
       <c r="D128" s="19">
         <f>'OPEX DATA 2'!U239</f>
-        <v>40.096153846153847</v>
+        <v>22.912087912087912</v>
       </c>
       <c r="E128" s="12">
         <f t="shared" si="4"/>
-        <v>1.2471587510467759E-4</v>
+        <v>7.1266214345530059E-5</v>
       </c>
       <c r="F128" s="12"/>
       <c r="G128" s="12"/>
@@ -9566,11 +9566,11 @@
       <c r="C130" s="36"/>
       <c r="D130" s="37">
         <f>SUM(D104:D129)</f>
-        <v>14144.820576923077</v>
+        <v>12216.326043956044</v>
       </c>
       <c r="E130" s="38">
         <f t="shared" si="4"/>
-        <v>4.3996331498983132E-2</v>
+        <v>3.7997903713704644E-2</v>
       </c>
       <c r="F130" s="38"/>
       <c r="G130" s="38"/>
@@ -9593,11 +9593,11 @@
       </c>
       <c r="D133" s="25">
         <f>'OPEX DATA 2'!U244</f>
-        <v>41.087500000000006</v>
+        <v>23.478571428571431</v>
       </c>
       <c r="E133" s="13">
         <f t="shared" ref="E133:E141" si="5">D133/D$36</f>
-        <v>1.2779937791601868E-4</v>
+        <v>7.3028215952010674E-5</v>
       </c>
     </row>
     <row r="134" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -9607,11 +9607,11 @@
       </c>
       <c r="D134" s="25">
         <f>'OPEX DATA 2'!U245</f>
-        <v>56.722307692307702</v>
+        <v>32.412747252747259</v>
       </c>
       <c r="E134" s="13">
         <f t="shared" si="5"/>
-        <v>1.7643019499940187E-4</v>
+        <v>1.008172542853725E-4</v>
       </c>
     </row>
     <row r="135" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -9635,11 +9635,11 @@
       </c>
       <c r="D136" s="25">
         <f>'OPEX DATA 2'!U247</f>
-        <v>238.67615384615385</v>
+        <v>136.38637362637363</v>
       </c>
       <c r="E136" s="13">
         <f t="shared" si="5"/>
-        <v>7.4238306017466202E-4</v>
+        <v>4.2421889152837833E-4</v>
       </c>
     </row>
     <row r="137" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -9649,11 +9649,11 @@
       </c>
       <c r="D137" s="25">
         <f>'OPEX DATA 2'!U248</f>
-        <v>46.737307692307695</v>
+        <v>26.707032967032969</v>
       </c>
       <c r="E137" s="13">
         <f t="shared" si="5"/>
-        <v>1.4537265223112813E-4</v>
+        <v>8.3070086989216072E-5</v>
       </c>
     </row>
     <row r="138" spans="2:7" x14ac:dyDescent="0.25">
@@ -9664,11 +9664,11 @@
       <c r="C138" s="15"/>
       <c r="D138" s="33">
         <f>'OPEX DATA 2'!U249</f>
-        <v>206.64576923076922</v>
+        <v>118.0832967032967</v>
       </c>
       <c r="E138" s="34">
         <f t="shared" si="5"/>
-        <v>6.427551142481158E-4</v>
+        <v>3.6728863671320902E-4</v>
       </c>
     </row>
     <row r="139" spans="2:7" x14ac:dyDescent="0.25">
@@ -9678,11 +9678,11 @@
       </c>
       <c r="D139" s="25">
         <f>'OPEX DATA 2'!U250</f>
-        <v>42.426153846153845</v>
+        <v>24.243516483516483</v>
       </c>
       <c r="E139" s="13">
         <f t="shared" si="5"/>
-        <v>1.3196315348725925E-4</v>
+        <v>7.5407516278433855E-5</v>
       </c>
     </row>
     <row r="140" spans="2:7" x14ac:dyDescent="0.25">
@@ -9708,11 +9708,11 @@
       <c r="C141" s="36"/>
       <c r="D141" s="37">
         <f>SUM(D133:D140)</f>
-        <v>632.29519230769233</v>
+        <v>361.31153846153848</v>
       </c>
       <c r="E141" s="38">
         <f t="shared" si="5"/>
-        <v>1.966703553056586E-3</v>
+        <v>1.1238306017466206E-3</v>
       </c>
       <c r="F141" s="38"/>
       <c r="G141" s="38"/>
@@ -9755,11 +9755,11 @@
       <c r="C145" s="44"/>
       <c r="D145" s="45">
         <f>'OPEX DATA 2'!U256</f>
-        <v>1801.5821153846152</v>
+        <v>1029.4754945054945</v>
       </c>
       <c r="E145" s="46">
         <f t="shared" si="6"/>
-        <v>5.603676875224309E-3</v>
+        <v>3.2021010715567481E-3</v>
       </c>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.25">
@@ -9785,11 +9785,11 @@
       <c r="C147" s="44"/>
       <c r="D147" s="45">
         <f>'OPEX DATA 2'!U258</f>
-        <v>533.03461538461534</v>
+        <v>304.59120879120877</v>
       </c>
       <c r="E147" s="46">
         <f t="shared" si="6"/>
-        <v>1.6579614786457709E-3</v>
+        <v>9.4740655922615478E-4</v>
       </c>
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.25">
@@ -9830,11 +9830,11 @@
       <c r="C150" s="44"/>
       <c r="D150" s="45">
         <f>'OPEX DATA 2'!U261</f>
-        <v>2000.7536538461538</v>
+        <v>1143.2878021978022</v>
       </c>
       <c r="E150" s="46">
         <f t="shared" si="6"/>
-        <v>6.2231839933006338E-3</v>
+        <v>3.5561051390289337E-3</v>
       </c>
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.25">
@@ -9845,11 +9845,11 @@
       <c r="C151" s="44"/>
       <c r="D151" s="45">
         <f>'OPEX DATA 2'!U262</f>
-        <v>161.95711538461541</v>
+        <v>92.546923076923093</v>
       </c>
       <c r="E151" s="46">
         <f t="shared" si="6"/>
-        <v>5.0375463572197639E-4</v>
+        <v>2.8785979184112935E-4</v>
       </c>
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.25">
@@ -9921,11 +9921,11 @@
       <c r="C157" s="44"/>
       <c r="D157" s="45">
         <f>'OPEX DATA 2'!U268</f>
-        <v>-3.7694230769230765</v>
+        <v>-2.1539560439560437</v>
       </c>
       <c r="E157" s="46">
         <f t="shared" si="7"/>
-        <v>-1.1724488575188419E-5</v>
+        <v>-6.6997077572505249E-6</v>
       </c>
     </row>
     <row r="158" spans="2:7" x14ac:dyDescent="0.25">
@@ -10145,11 +10145,11 @@
       <c r="C172" s="36"/>
       <c r="D172" s="37">
         <f>SUM(D155:D171)</f>
-        <v>-10613.269423076923</v>
+        <v>-10611.653956043956</v>
       </c>
       <c r="E172" s="38">
         <f t="shared" si="7"/>
-        <v>-3.3011724488575186E-2</v>
+        <v>-3.3006699707757249E-2</v>
       </c>
       <c r="F172" s="38"/>
       <c r="G172" s="38"/>
@@ -10192,11 +10192,11 @@
       <c r="C176" s="44"/>
       <c r="D176" s="45">
         <f>'OPEX DATA 2'!U289</f>
-        <v>250.48826923076922</v>
+        <v>143.13615384615383</v>
       </c>
       <c r="E176" s="46">
         <f t="shared" si="8"/>
-        <v>7.7912369900705824E-4</v>
+        <v>4.4521354228974753E-4</v>
       </c>
     </row>
     <row r="177" spans="2:5" x14ac:dyDescent="0.25">
@@ -10207,11 +10207,11 @@
       <c r="C177" s="44"/>
       <c r="D177" s="45">
         <f>'OPEX DATA 2'!U290</f>
-        <v>3494.1401923076924</v>
+        <v>1996.6515384615384</v>
       </c>
       <c r="E177" s="46">
         <f t="shared" si="8"/>
-        <v>1.0868243210910396E-2</v>
+        <v>6.2104246919487977E-3</v>
       </c>
     </row>
     <row r="178" spans="2:5" x14ac:dyDescent="0.25">
@@ -10237,11 +10237,11 @@
       <c r="C179" s="44"/>
       <c r="D179" s="45">
         <f>'OPEX DATA 2'!U292</f>
-        <v>145.01365384615386</v>
+        <v>82.864945054945068</v>
       </c>
       <c r="E179" s="46">
         <f t="shared" si="8"/>
-        <v>4.5105335566455323E-4</v>
+        <v>2.5774477466545902E-4</v>
       </c>
     </row>
     <row r="180" spans="2:5" x14ac:dyDescent="0.25">
@@ -10252,11 +10252,11 @@
       <c r="C180" s="44"/>
       <c r="D180" s="45">
         <f>'OPEX DATA 2'!U293</f>
-        <v>3.463461538461539</v>
+        <v>1.9791208791208794</v>
       </c>
       <c r="E180" s="46">
         <f t="shared" si="8"/>
-        <v>1.0772819715276948E-5</v>
+        <v>6.1558969801582565E-6</v>
       </c>
     </row>
     <row r="181" spans="2:5" x14ac:dyDescent="0.25">
@@ -10267,11 +10267,11 @@
       <c r="C181" s="44"/>
       <c r="D181" s="45">
         <f>'OPEX DATA 2'!U294</f>
-        <v>94.820384615384626</v>
+        <v>54.183076923076932</v>
       </c>
       <c r="E181" s="46">
         <f t="shared" si="8"/>
-        <v>2.9493121186744829E-4</v>
+        <v>1.6853212106711333E-4</v>
       </c>
     </row>
     <row r="182" spans="2:5" x14ac:dyDescent="0.25">
@@ -10282,11 +10282,11 @@
       <c r="C182" s="44"/>
       <c r="D182" s="45">
         <f>'OPEX DATA 2'!U295</f>
-        <v>29.668846153846154</v>
+        <v>16.953626373626374</v>
       </c>
       <c r="E182" s="46">
         <f t="shared" si="8"/>
-        <v>9.2282569685369064E-5</v>
+        <v>5.2732896963068038E-5</v>
       </c>
     </row>
     <row r="183" spans="2:5" x14ac:dyDescent="0.25">
@@ -10312,11 +10312,11 @@
       <c r="C184" s="44"/>
       <c r="D184" s="45">
         <f>'OPEX DATA 2'!U297</f>
-        <v>11.57076923076923</v>
+        <v>6.6118681318681309</v>
       </c>
       <c r="E184" s="46">
         <f t="shared" si="8"/>
-        <v>3.59899509510707E-5</v>
+        <v>2.0565686257754684E-5</v>
       </c>
     </row>
     <row r="185" spans="2:5" x14ac:dyDescent="0.25">
@@ -10567,11 +10567,11 @@
       <c r="C201" s="36"/>
       <c r="D201" s="37">
         <f>SUM(D175:D200)</f>
-        <v>4029.165576923077</v>
+        <v>2302.3803296703295</v>
       </c>
       <c r="E201" s="38">
         <f t="shared" si="8"/>
-        <v>1.2532396817801172E-2</v>
+        <v>7.1613696101720976E-3</v>
       </c>
       <c r="F201" s="38"/>
       <c r="G201" s="38"/>
@@ -10589,21 +10589,21 @@
       <c r="C203" s="36"/>
       <c r="D203" s="37">
         <f>D43-D50-D101-D130-D141-D152-D172-D201</f>
-        <v>116921.17980769232</v>
+        <v>123042.05120879122</v>
       </c>
       <c r="E203" s="38">
         <f>D203/D36</f>
-        <v>0.36367396518722339</v>
+        <v>0.38271244543947502</v>
       </c>
       <c r="F203" s="38"/>
       <c r="G203" s="38"/>
     </row>
     <row r="205" spans="2:175" x14ac:dyDescent="0.25">
-      <c r="D205" s="77">
+      <c r="D205" s="84">
         <f>D2</f>
         <v>46025</v>
       </c>
-      <c r="E205" s="77"/>
+      <c r="E205" s="84"/>
     </row>
     <row r="206" spans="2:175" x14ac:dyDescent="0.25">
       <c r="B206" s="8" t="s">
@@ -10619,7 +10619,7 @@
       <c r="C207" s="50"/>
       <c r="D207" s="51">
         <f>E203</f>
-        <v>0.36367396518722339</v>
+        <v>0.38271244543947502</v>
       </c>
     </row>
     <row r="208" spans="2:175" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -18321,12 +18321,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D8:E8"/>
     <mergeCell ref="D205:E205"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D11:E11"/>
@@ -18334,6 +18328,12 @@
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D8:E8"/>
   </mergeCells>
   <conditionalFormatting sqref="D30">
     <cfRule type="cellIs" dxfId="1" priority="1" stopIfTrue="1" operator="lessThan">
@@ -18484,8 +18484,8 @@
         <v>670788.38</v>
       </c>
       <c r="U8" s="65">
-        <f>(T8/$V$1)/4</f>
-        <v>12899.776538461538</v>
+        <f>(T8/$V$1)/7</f>
+        <v>7371.3008791208786</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -18521,7 +18521,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="65">
-        <f t="shared" ref="U9:U72" si="1">(T9/$V$1)/4</f>
+        <f t="shared" ref="U9:U72" si="1">(T9/$V$1)/7</f>
         <v>0</v>
       </c>
     </row>
@@ -18562,7 +18562,7 @@
       </c>
       <c r="U10" s="65">
         <f t="shared" si="1"/>
-        <v>12899.776538461538</v>
+        <v>7371.3008791208786</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -18599,7 +18599,7 @@
       </c>
       <c r="U11" s="65">
         <f t="shared" si="1"/>
-        <v>2192.7884615384614</v>
+        <v>1253.0219780219779</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -18695,7 +18695,7 @@
       </c>
       <c r="U14" s="65">
         <f t="shared" si="1"/>
-        <v>39394.725576923076</v>
+        <v>22511.271758241757</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="U15" s="65">
         <f t="shared" si="1"/>
-        <v>328.53846153846155</v>
+        <v>187.73626373626374</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="U16" s="65">
         <f t="shared" si="1"/>
-        <v>9547.5576923076915</v>
+        <v>5455.7472527472519</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="U17" s="65">
         <f t="shared" si="1"/>
-        <v>1209.7307692307693</v>
+        <v>691.27472527472526</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="U19" s="65">
         <f t="shared" si="1"/>
-        <v>50480.552499999998</v>
+        <v>28846.03</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="U22" s="65">
         <f t="shared" si="1"/>
-        <v>1515.7048076923077</v>
+        <v>866.11703296703297</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="U23" s="65">
         <f t="shared" si="1"/>
-        <v>24.96365384615385</v>
+        <v>14.264945054945057</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="U26" s="65">
         <f t="shared" si="1"/>
-        <v>2769.0149999999999</v>
+        <v>1582.2942857142857</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="U30" s="65">
         <f t="shared" si="1"/>
-        <v>4309.6834615384614</v>
+        <v>2462.6762637362635</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -19621,7 +19621,7 @@
       </c>
       <c r="U40" s="65">
         <f t="shared" si="1"/>
-        <v>-7.1057692307692308</v>
+        <v>-4.0604395604395602</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="U41" s="65">
         <f t="shared" si="1"/>
-        <v>-76.92307692307692</v>
+        <v>-43.956043956043956</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -19695,7 +19695,7 @@
       </c>
       <c r="U42" s="65">
         <f t="shared" si="1"/>
-        <v>-202.30769230769232</v>
+        <v>-115.60439560439561</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="U43" s="65">
         <f t="shared" si="1"/>
-        <v>-1072.3548076923075</v>
+        <v>-612.7741758241757</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="U44" s="65">
         <f t="shared" si="1"/>
-        <v>-92.269230769230774</v>
+        <v>-52.72527472527473</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -19843,7 +19843,7 @@
       </c>
       <c r="U46" s="65">
         <f t="shared" si="1"/>
-        <v>-1323.6540384615384</v>
+        <v>-756.3737362637363</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -19880,7 +19880,7 @@
       </c>
       <c r="U47" s="65">
         <f t="shared" si="1"/>
-        <v>-328.96153846153845</v>
+        <v>-187.97802197802199</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="U48" s="65">
         <f t="shared" si="1"/>
-        <v>-128.30769230769232</v>
+        <v>-73.318681318681328</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="U50" s="65">
         <f t="shared" si="1"/>
-        <v>-161.67307692307693</v>
+        <v>-92.384615384615387</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="U51" s="65">
         <f t="shared" si="1"/>
-        <v>-3393.5569230769229</v>
+        <v>-1939.1753846153845</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -20071,7 +20071,7 @@
       </c>
       <c r="U52" s="65">
         <f t="shared" si="1"/>
-        <v>66489.244038461547</v>
+        <v>37993.853736263743</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -20189,7 +20189,7 @@
       </c>
       <c r="U56" s="65">
         <f t="shared" si="1"/>
-        <v>505.92442307692306</v>
+        <v>289.09967032967035</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="U57" s="65">
         <f t="shared" si="1"/>
-        <v>200.64461538461541</v>
+        <v>114.65406593406594</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -20263,7 +20263,7 @@
       </c>
       <c r="U58" s="65">
         <f t="shared" si="1"/>
-        <v>700.77980769230771</v>
+        <v>400.44560439560439</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="U59" s="65">
         <f t="shared" si="1"/>
-        <v>56.907307692307697</v>
+        <v>32.518461538461544</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -20337,7 +20337,7 @@
       </c>
       <c r="U60" s="65">
         <f t="shared" si="1"/>
-        <v>1259.9659615384614</v>
+        <v>719.98054945054935</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="U61" s="65">
         <f t="shared" si="1"/>
-        <v>442.44865384615389</v>
+        <v>252.82780219780221</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -20411,7 +20411,7 @@
       </c>
       <c r="U62" s="65">
         <f t="shared" si="1"/>
-        <v>90.053269230769246</v>
+        <v>51.459010989010999</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="U63" s="65">
         <f t="shared" si="1"/>
-        <v>115.24499999999999</v>
+        <v>65.854285714285709</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="U65" s="65">
         <f t="shared" si="1"/>
-        <v>3371.9690384615383</v>
+        <v>1926.8394505494505</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -20562,7 +20562,7 @@
       </c>
       <c r="U66" s="65">
         <f t="shared" si="1"/>
-        <v>455.79365384615386</v>
+        <v>260.45351648351647</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="U69" s="65">
         <f t="shared" si="1"/>
-        <v>44.180384615384618</v>
+        <v>25.245934065934069</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -20732,7 +20732,7 @@
       </c>
       <c r="U71" s="65">
         <f t="shared" si="1"/>
-        <v>1850.416346153846</v>
+        <v>1057.3807692307691</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="U72" s="65">
         <f t="shared" si="1"/>
-        <v>1.7307692307692308</v>
+        <v>0.98901098901098905</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -20805,8 +20805,8 @@
         <v>188460.25</v>
       </c>
       <c r="U73" s="65">
-        <f t="shared" ref="U73:U136" si="3">(T73/$V$1)/4</f>
-        <v>3624.2355769230771</v>
+        <f t="shared" ref="U73:U136" si="3">(T73/$V$1)/7</f>
+        <v>2070.9917582417584</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -20880,7 +20880,7 @@
       </c>
       <c r="U75" s="65">
         <f t="shared" si="3"/>
-        <v>318.34326923076918</v>
+        <v>181.91043956043953</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="U76" s="65">
         <f t="shared" si="3"/>
-        <v>5838.9063461538462</v>
+        <v>3336.517912087912</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -21173,7 +21173,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="65">
-        <f t="shared" si="3"/>
+        <f>(T84/$V$1)/4</f>
         <v>0</v>
       </c>
     </row>
@@ -21210,7 +21210,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="U85:U148" si="4">(T85/$V$1)/4</f>
         <v>0</v>
       </c>
     </row>
@@ -21247,7 +21247,7 @@
         <v>0</v>
       </c>
       <c r="U86" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21284,7 +21284,7 @@
         <v>0</v>
       </c>
       <c r="U87" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21321,7 +21321,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21358,7 +21358,7 @@
         <v>0</v>
       </c>
       <c r="U89" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21395,7 +21395,7 @@
         <v>0</v>
       </c>
       <c r="U90" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21432,7 +21432,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21469,7 +21469,7 @@
         <v>0</v>
       </c>
       <c r="U92" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21506,7 +21506,7 @@
         <v>0</v>
       </c>
       <c r="U93" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21543,7 +21543,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21580,7 +21580,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21654,7 +21654,7 @@
         <v>53195.32</v>
       </c>
       <c r="U97" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1022.9869230769231</v>
       </c>
     </row>
@@ -21691,7 +21691,7 @@
         <v>13234.720000000001</v>
       </c>
       <c r="U98" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>254.51384615384617</v>
       </c>
     </row>
@@ -21728,7 +21728,7 @@
         <v>0</v>
       </c>
       <c r="U99" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21765,7 +21765,7 @@
         <v>0</v>
       </c>
       <c r="U100" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21802,7 +21802,7 @@
         <v>0</v>
       </c>
       <c r="U101" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21839,7 +21839,7 @@
         <v>0</v>
       </c>
       <c r="U102" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21876,7 +21876,7 @@
         <v>0</v>
       </c>
       <c r="U103" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21913,7 +21913,7 @@
         <v>0</v>
       </c>
       <c r="U104" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21950,7 +21950,7 @@
         <v>0</v>
       </c>
       <c r="U105" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21987,7 +21987,7 @@
         <v>0</v>
       </c>
       <c r="U106" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
         <v>0</v>
       </c>
       <c r="U107" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22061,7 +22061,7 @@
         <v>0</v>
       </c>
       <c r="U108" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22098,7 +22098,7 @@
         <v>0</v>
       </c>
       <c r="U109" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22135,7 +22135,7 @@
         <v>12942.869999999999</v>
       </c>
       <c r="U110" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>248.90134615384613</v>
       </c>
     </row>
@@ -22172,7 +22172,7 @@
         <v>0</v>
       </c>
       <c r="U111" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22209,7 +22209,7 @@
         <v>12178.16</v>
       </c>
       <c r="U112" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>234.19538461538463</v>
       </c>
     </row>
@@ -22246,7 +22246,7 @@
         <v>0</v>
       </c>
       <c r="U113" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22283,7 +22283,7 @@
         <v>2005.4099999999999</v>
       </c>
       <c r="U114" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>38.565576923076918</v>
       </c>
     </row>
@@ -22320,7 +22320,7 @@
         <v>0</v>
       </c>
       <c r="U115" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22357,7 +22357,7 @@
         <v>0</v>
       </c>
       <c r="U116" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22394,7 +22394,7 @@
         <v>0</v>
       </c>
       <c r="U117" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22431,7 +22431,7 @@
         <v>13829.2</v>
       </c>
       <c r="U118" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>265.94615384615383</v>
       </c>
     </row>
@@ -22471,7 +22471,7 @@
         <v>107385.68000000001</v>
       </c>
       <c r="U119" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2065.1092307692311</v>
       </c>
     </row>
@@ -22511,7 +22511,7 @@
         <v>107385.68000000001</v>
       </c>
       <c r="U120" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2065.1092307692311</v>
       </c>
     </row>
@@ -22533,7 +22533,7 @@
         <v>0</v>
       </c>
       <c r="U121" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
         <v>0</v>
       </c>
       <c r="U122" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22607,7 +22607,7 @@
         <v>59432.79</v>
       </c>
       <c r="U123" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1142.9382692307693</v>
       </c>
     </row>
@@ -22644,7 +22644,7 @@
         <v>4442.32</v>
       </c>
       <c r="U124" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>85.42923076923077</v>
       </c>
     </row>
@@ -22681,7 +22681,7 @@
         <v>0</v>
       </c>
       <c r="U125" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="U126" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
         <v>0</v>
       </c>
       <c r="U127" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22792,7 +22792,7 @@
         <v>0</v>
       </c>
       <c r="U128" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22829,7 +22829,7 @@
         <v>0</v>
       </c>
       <c r="U129" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22866,7 +22866,7 @@
         <v>0</v>
       </c>
       <c r="U130" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22903,7 +22903,7 @@
         <v>0</v>
       </c>
       <c r="U131" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22940,7 +22940,7 @@
         <v>0</v>
       </c>
       <c r="U132" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -22977,7 +22977,7 @@
         <v>0</v>
       </c>
       <c r="U133" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23014,7 +23014,7 @@
         <v>0</v>
       </c>
       <c r="U134" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
         <v>0</v>
       </c>
       <c r="U135" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23088,7 +23088,7 @@
         <v>0</v>
       </c>
       <c r="U136" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23121,11 +23121,11 @@
         <v>0</v>
       </c>
       <c r="T137" s="65">
-        <f t="shared" ref="T137:T200" si="4">IFERROR(B137+E137+H137+K137+N137+Q137, "NA")</f>
+        <f t="shared" ref="T137:T200" si="5">IFERROR(B137+E137+H137+K137+N137+Q137, "NA")</f>
         <v>0</v>
       </c>
       <c r="U137" s="65">
-        <f t="shared" ref="U137:U200" si="5">(T137/$V$1)/4</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23158,11 +23158,11 @@
         <v>0</v>
       </c>
       <c r="T138" s="65">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U138" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U138" s="65">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -23195,11 +23195,11 @@
         <v>3.5683466654110693E-2</v>
       </c>
       <c r="T139" s="65">
+        <f t="shared" si="5"/>
+        <v>121960.68000000001</v>
+      </c>
+      <c r="U139" s="65">
         <f t="shared" si="4"/>
-        <v>121960.68000000001</v>
-      </c>
-      <c r="U139" s="65">
-        <f t="shared" si="5"/>
         <v>2345.3976923076925</v>
       </c>
     </row>
@@ -23232,11 +23232,11 @@
         <v>0</v>
       </c>
       <c r="T140" s="65">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U140" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U140" s="65">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -23269,11 +23269,11 @@
         <v>1.3697219054624147E-2</v>
       </c>
       <c r="T141" s="65">
+        <f t="shared" si="5"/>
+        <v>38801.049999999996</v>
+      </c>
+      <c r="U141" s="65">
         <f t="shared" si="4"/>
-        <v>38801.049999999996</v>
-      </c>
-      <c r="U141" s="65">
-        <f t="shared" si="5"/>
         <v>746.17403846153843</v>
       </c>
     </row>
@@ -23306,11 +23306,11 @@
         <v>6.8043366631218493E-3</v>
       </c>
       <c r="T142" s="65">
+        <f t="shared" si="5"/>
+        <v>25443.18</v>
+      </c>
+      <c r="U142" s="65">
         <f t="shared" si="4"/>
-        <v>25443.18</v>
-      </c>
-      <c r="U142" s="65">
-        <f t="shared" si="5"/>
         <v>489.29192307692307</v>
       </c>
     </row>
@@ -23346,11 +23346,11 @@
         <v>7.8434525288164622E-2</v>
       </c>
       <c r="T143" s="65">
+        <f t="shared" si="5"/>
+        <v>250080.02</v>
+      </c>
+      <c r="U143" s="65">
         <f t="shared" si="4"/>
-        <v>250080.02</v>
-      </c>
-      <c r="U143" s="65">
-        <f t="shared" si="5"/>
         <v>4809.2311538461536</v>
       </c>
     </row>
@@ -23368,11 +23368,11 @@
       <c r="Q144" s="58"/>
       <c r="R144" s="59"/>
       <c r="T144" s="65">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U144" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U144" s="65">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -23405,11 +23405,11 @@
         <v>0</v>
       </c>
       <c r="T145" s="65">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U145" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U145" s="65">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -23442,11 +23442,11 @@
         <v>1.8308996118306331E-2</v>
       </c>
       <c r="T146" s="65">
+        <f t="shared" si="5"/>
+        <v>61338.83</v>
+      </c>
+      <c r="U146" s="65">
         <f t="shared" si="4"/>
-        <v>61338.83</v>
-      </c>
-      <c r="U146" s="65">
-        <f t="shared" si="5"/>
         <v>1179.5928846153847</v>
       </c>
     </row>
@@ -23479,11 +23479,11 @@
         <v>9.2275752282543061E-3</v>
       </c>
       <c r="T147" s="65">
+        <f t="shared" si="5"/>
+        <v>19645.75</v>
+      </c>
+      <c r="U147" s="65">
         <f t="shared" si="4"/>
-        <v>19645.75</v>
-      </c>
-      <c r="U147" s="65">
-        <f t="shared" si="5"/>
         <v>377.80288461538464</v>
       </c>
     </row>
@@ -23516,11 +23516,11 @@
         <v>3.7380389342731406E-3</v>
       </c>
       <c r="T148" s="65">
+        <f t="shared" si="5"/>
+        <v>13872.619999999999</v>
+      </c>
+      <c r="U148" s="65">
         <f t="shared" si="4"/>
-        <v>13872.619999999999</v>
-      </c>
-      <c r="U148" s="65">
-        <f t="shared" si="5"/>
         <v>266.78115384615381</v>
       </c>
     </row>
@@ -23553,11 +23553,11 @@
         <v>6.6704629843942435E-3</v>
       </c>
       <c r="T149" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13420.07</v>
       </c>
       <c r="U149" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="U149:U157" si="6">(T149/$V$1)/4</f>
         <v>258.07826923076925</v>
       </c>
     </row>
@@ -23590,11 +23590,11 @@
         <v>9.5434127787851208E-3</v>
       </c>
       <c r="T150" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>28456.550000000003</v>
       </c>
       <c r="U150" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>547.24134615384617</v>
       </c>
     </row>
@@ -23630,11 +23630,11 @@
         <v>4.7488486044013144E-2</v>
       </c>
       <c r="T151" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>136733.82</v>
       </c>
       <c r="U151" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2629.4965384615384</v>
       </c>
     </row>
@@ -23667,11 +23667,11 @@
         <v>0</v>
       </c>
       <c r="T152" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U152" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -23704,11 +23704,11 @@
         <v>3.7628719492285656E-3</v>
       </c>
       <c r="T153" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>18584.71</v>
       </c>
       <c r="U153" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>357.39826923076919</v>
       </c>
     </row>
@@ -23741,11 +23741,11 @@
         <v>3.3797171849254401E-4</v>
       </c>
       <c r="T154" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>687.90000000000009</v>
       </c>
       <c r="U154" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>13.228846153846156</v>
       </c>
     </row>
@@ -23778,11 +23778,11 @@
         <v>-2.9587695061770224E-5</v>
       </c>
       <c r="T155" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-73.56</v>
       </c>
       <c r="U155" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.4146153846153846</v>
       </c>
     </row>
@@ -23815,11 +23815,11 @@
         <v>0</v>
       </c>
       <c r="T156" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U156" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -23855,11 +23855,11 @@
         <v>0.30238977557937069</v>
       </c>
       <c r="T157" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1016065.3600000003</v>
       </c>
       <c r="U157" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>19539.718461538469</v>
       </c>
     </row>
@@ -23877,11 +23877,11 @@
       <c r="Q158" s="58"/>
       <c r="R158" s="59"/>
       <c r="T158" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U158" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="U137:U200" si="7">(T158/$V$1)/7</f>
         <v>0</v>
       </c>
     </row>
@@ -23899,11 +23899,11 @@
       <c r="Q159" s="58"/>
       <c r="R159" s="59"/>
       <c r="T159" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U159" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -23936,11 +23936,11 @@
         <v>0</v>
       </c>
       <c r="T160" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U160" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -23973,12 +23973,12 @@
         <v>0</v>
       </c>
       <c r="T161" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12.56</v>
       </c>
       <c r="U161" s="65">
-        <f t="shared" si="5"/>
-        <v>0.24153846153846154</v>
+        <f t="shared" si="7"/>
+        <v>0.13802197802197802</v>
       </c>
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
@@ -24010,12 +24010,12 @@
         <v>-3.2750327137840251E-3</v>
       </c>
       <c r="T162" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16422.46</v>
       </c>
       <c r="U162" s="65">
-        <f t="shared" si="5"/>
-        <v>315.81653846153847</v>
+        <f t="shared" si="7"/>
+        <v>180.4665934065934</v>
       </c>
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
@@ -24047,12 +24047,12 @@
         <v>1.0126110146484628E-3</v>
       </c>
       <c r="T163" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6317.7099999999991</v>
       </c>
       <c r="U163" s="65">
-        <f t="shared" si="5"/>
-        <v>121.49442307692306</v>
+        <f t="shared" si="7"/>
+        <v>69.425384615384601</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
@@ -24084,12 +24084,12 @@
         <v>1.9362325307732181E-3</v>
       </c>
       <c r="T164" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1990.94</v>
       </c>
       <c r="U164" s="65">
-        <f t="shared" si="5"/>
-        <v>38.287307692307692</v>
+        <f t="shared" si="7"/>
+        <v>21.87846153846154</v>
       </c>
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
@@ -24121,12 +24121,12 @@
         <v>6.5234211059054463E-5</v>
       </c>
       <c r="T165" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2832.7200000000003</v>
       </c>
       <c r="U165" s="65">
-        <f t="shared" si="5"/>
-        <v>54.47538461538462</v>
+        <f t="shared" si="7"/>
+        <v>31.12879120879121</v>
       </c>
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
@@ -24158,12 +24158,12 @@
         <v>3.1651497923930066E-3</v>
       </c>
       <c r="T166" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9077.32</v>
       </c>
       <c r="U166" s="65">
-        <f t="shared" si="5"/>
-        <v>174.56384615384616</v>
+        <f t="shared" si="7"/>
+        <v>99.750769230769237</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
@@ -24195,12 +24195,12 @@
         <v>3.257607943260962E-3</v>
       </c>
       <c r="T167" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7677.9400000000005</v>
       </c>
       <c r="U167" s="65">
-        <f t="shared" si="5"/>
-        <v>147.65269230769232</v>
+        <f t="shared" si="7"/>
+        <v>84.37296703296704</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
@@ -24232,12 +24232,12 @@
         <v>4.363709553600474E-3</v>
       </c>
       <c r="T168" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13096.880000000001</v>
       </c>
       <c r="U168" s="65">
-        <f t="shared" si="5"/>
-        <v>251.86307692307693</v>
+        <f t="shared" si="7"/>
+        <v>143.92175824175825</v>
       </c>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
@@ -24269,12 +24269,12 @@
         <v>0</v>
       </c>
       <c r="T169" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1154.21</v>
       </c>
       <c r="U169" s="65">
-        <f t="shared" si="5"/>
-        <v>22.196346153846154</v>
+        <f t="shared" si="7"/>
+        <v>12.683626373626373</v>
       </c>
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
@@ -24306,12 +24306,12 @@
         <v>3.5896023496198156E-3</v>
       </c>
       <c r="T170" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19516.61</v>
       </c>
       <c r="U170" s="65">
-        <f t="shared" si="5"/>
-        <v>375.3194230769231</v>
+        <f t="shared" si="7"/>
+        <v>214.46824175824176</v>
       </c>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
@@ -24343,12 +24343,12 @@
         <v>3.2470389686245727E-3</v>
       </c>
       <c r="T171" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10142.790000000001</v>
       </c>
       <c r="U171" s="65">
-        <f t="shared" si="5"/>
-        <v>195.05365384615385</v>
+        <f t="shared" si="7"/>
+        <v>111.45923076923077</v>
       </c>
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
@@ -24380,11 +24380,11 @@
         <v>0</v>
       </c>
       <c r="T172" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U172" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -24417,11 +24417,11 @@
         <v>0</v>
       </c>
       <c r="T173" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U173" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -24454,11 +24454,11 @@
         <v>0</v>
       </c>
       <c r="T174" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U174" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
         <v>3.1430518505654215E-3</v>
       </c>
       <c r="T175" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8315.32</v>
       </c>
       <c r="U175" s="65">
-        <f t="shared" si="5"/>
-        <v>159.91</v>
+        <f t="shared" si="7"/>
+        <v>91.377142857142857</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
@@ -24528,12 +24528,12 @@
         <v>2.5226611902895162E-3</v>
       </c>
       <c r="T176" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14795.849999999999</v>
       </c>
       <c r="U176" s="65">
-        <f t="shared" si="5"/>
-        <v>284.53557692307692</v>
+        <f t="shared" si="7"/>
+        <v>162.59175824175824</v>
       </c>
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
@@ -24565,12 +24565,12 @@
         <v>3.8123659050022345E-3</v>
       </c>
       <c r="T177" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10364.11</v>
       </c>
       <c r="U177" s="65">
-        <f t="shared" si="5"/>
-        <v>199.30980769230771</v>
+        <f t="shared" si="7"/>
+        <v>113.89131868131869</v>
       </c>
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
@@ -24602,12 +24602,12 @@
         <v>1.9330265179015111E-4</v>
       </c>
       <c r="T178" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>790.2</v>
       </c>
       <c r="U178" s="65">
-        <f t="shared" si="5"/>
-        <v>15.196153846153846</v>
+        <f t="shared" si="7"/>
+        <v>8.6835164835164829</v>
       </c>
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
@@ -24639,12 +24639,12 @@
         <v>1.8915928769747898E-3</v>
       </c>
       <c r="T179" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8573.85</v>
       </c>
       <c r="U179" s="65">
-        <f t="shared" si="5"/>
-        <v>164.88173076923078</v>
+        <f t="shared" si="7"/>
+        <v>94.218131868131877</v>
       </c>
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
@@ -24676,12 +24676,12 @@
         <v>1.1475080816656248E-2</v>
       </c>
       <c r="T180" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>18641.900000000001</v>
       </c>
       <c r="U180" s="65">
-        <f t="shared" si="5"/>
-        <v>358.49807692307695</v>
+        <f t="shared" si="7"/>
+        <v>204.85604395604398</v>
       </c>
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
@@ -24713,11 +24713,11 @@
         <v>0</v>
       </c>
       <c r="T181" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U181" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -24750,12 +24750,12 @@
         <v>2.3755287464653598E-4</v>
       </c>
       <c r="T182" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>610.01</v>
       </c>
       <c r="U182" s="65">
-        <f t="shared" si="5"/>
-        <v>11.730961538461539</v>
+        <f t="shared" si="7"/>
+        <v>6.7034065934065934</v>
       </c>
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
@@ -24787,12 +24787,12 @@
         <v>2.2992636775595846E-3</v>
       </c>
       <c r="T183" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6846.89</v>
       </c>
       <c r="U183" s="65">
-        <f t="shared" si="5"/>
-        <v>131.67096153846154</v>
+        <f t="shared" si="7"/>
+        <v>75.240549450549452</v>
       </c>
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
@@ -24824,12 +24824,12 @@
         <v>1.9405434407363044E-4</v>
       </c>
       <c r="T184" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1111.3799999999999</v>
       </c>
       <c r="U184" s="65">
-        <f t="shared" si="5"/>
-        <v>21.372692307692304</v>
+        <f t="shared" si="7"/>
+        <v>12.212967032967031</v>
       </c>
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
@@ -24861,12 +24861,12 @@
         <v>0</v>
       </c>
       <c r="T185" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2047</v>
       </c>
       <c r="U185" s="65">
-        <f t="shared" si="5"/>
-        <v>39.365384615384613</v>
+        <f t="shared" si="7"/>
+        <v>22.494505494505493</v>
       </c>
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
@@ -24898,11 +24898,11 @@
         <v>0</v>
       </c>
       <c r="T186" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U186" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -24935,12 +24935,12 @@
         <v>9.2038833365244027E-4</v>
       </c>
       <c r="T187" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2153.0699999999997</v>
       </c>
       <c r="U187" s="65">
-        <f t="shared" si="5"/>
-        <v>41.405192307692303</v>
+        <f t="shared" si="7"/>
+        <v>23.660109890109887</v>
       </c>
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
@@ -24972,12 +24972,12 @@
         <v>2.4143088230660636E-3</v>
       </c>
       <c r="T188" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5094.99</v>
       </c>
       <c r="U188" s="65">
-        <f t="shared" si="5"/>
-        <v>97.980576923076924</v>
+        <f t="shared" si="7"/>
+        <v>55.988901098901103</v>
       </c>
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
@@ -25009,12 +25009,12 @@
         <v>5.6204213166419249E-3</v>
       </c>
       <c r="T189" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>25120.82</v>
       </c>
       <c r="U189" s="65">
-        <f t="shared" si="5"/>
-        <v>483.09269230769229</v>
+        <f t="shared" si="7"/>
+        <v>276.05296703296705</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
@@ -25046,11 +25046,11 @@
         <v>0</v>
       </c>
       <c r="T190" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U190" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -25083,11 +25083,11 @@
         <v>0</v>
       </c>
       <c r="T191" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U191" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -25120,12 +25120,12 @@
         <v>8.0093265631398024E-4</v>
       </c>
       <c r="T192" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4870.91</v>
       </c>
       <c r="U192" s="65">
-        <f t="shared" si="5"/>
-        <v>93.671346153846144</v>
+        <f t="shared" si="7"/>
+        <v>53.526483516483509</v>
       </c>
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
@@ -25157,12 +25157,12 @@
         <v>1.3614768373313355E-2</v>
       </c>
       <c r="T193" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>38083.149999999994</v>
       </c>
       <c r="U193" s="65">
-        <f t="shared" si="5"/>
-        <v>732.3682692307691</v>
+        <f t="shared" si="7"/>
+        <v>418.49615384615379</v>
       </c>
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
@@ -25194,12 +25194,12 @@
         <v>9.5192590038448884E-3</v>
       </c>
       <c r="T194" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>22692.35</v>
       </c>
       <c r="U194" s="65">
-        <f t="shared" si="5"/>
-        <v>436.39134615384614</v>
+        <f t="shared" si="7"/>
+        <v>249.3664835164835</v>
       </c>
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
@@ -25231,12 +25231,12 @@
         <v>1.4770843935703938E-3</v>
       </c>
       <c r="T195" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4571.09</v>
       </c>
       <c r="U195" s="65">
-        <f t="shared" si="5"/>
-        <v>87.905576923076922</v>
+        <f t="shared" si="7"/>
+        <v>50.231758241758243</v>
       </c>
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
@@ -25268,12 +25268,12 @@
         <v>0.12701723982705174</v>
       </c>
       <c r="T196" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>404107.48</v>
       </c>
       <c r="U196" s="65">
-        <f t="shared" si="5"/>
-        <v>7771.2976923076922</v>
+        <f t="shared" si="7"/>
+        <v>4440.7415384615388</v>
       </c>
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
@@ -25305,12 +25305,12 @@
         <v>1.4180629645169636E-3</v>
       </c>
       <c r="T197" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1585.23</v>
       </c>
       <c r="U197" s="65">
-        <f t="shared" si="5"/>
-        <v>30.485192307692309</v>
+        <f t="shared" si="7"/>
+        <v>17.420109890109892</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
@@ -25342,11 +25342,11 @@
         <v>0</v>
       </c>
       <c r="T198" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U198" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -25379,11 +25379,11 @@
         <v>0</v>
       </c>
       <c r="T199" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U199" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -25416,11 +25416,11 @@
         <v>0</v>
       </c>
       <c r="T200" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U200" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -25453,12 +25453,12 @@
         <v>2.9065133076749061E-4</v>
       </c>
       <c r="T201" s="65">
-        <f t="shared" ref="T201:T264" si="6">IFERROR(B201+E201+H201+K201+N201+Q201, "NA")</f>
+        <f t="shared" ref="T201:T264" si="8">IFERROR(B201+E201+H201+K201+N201+Q201, "NA")</f>
         <v>1964.85</v>
       </c>
       <c r="U201" s="65">
-        <f t="shared" ref="U201:U264" si="7">(T201/$V$1)/4</f>
-        <v>37.785576923076924</v>
+        <f t="shared" ref="U201:U264" si="9">(T201/$V$1)/7</f>
+        <v>21.591758241758242</v>
       </c>
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
@@ -25490,11 +25490,11 @@
         <v>0</v>
       </c>
       <c r="T202" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U202" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -25527,11 +25527,11 @@
         <v>0</v>
       </c>
       <c r="T203" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U203" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -25564,11 +25564,11 @@
         <v>0</v>
       </c>
       <c r="T204" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U204" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -25601,11 +25601,11 @@
         <v>0</v>
       </c>
       <c r="T205" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U205" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -25638,11 +25638,11 @@
         <v>0</v>
       </c>
       <c r="T206" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U206" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -25675,11 +25675,11 @@
         <v>0</v>
       </c>
       <c r="T207" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U207" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -25712,11 +25712,11 @@
         <v>0</v>
       </c>
       <c r="T208" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U208" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -25752,12 +25752,12 @@
         <v>0.20622419686049287</v>
       </c>
       <c r="T209" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>670582.59</v>
       </c>
       <c r="U209" s="65">
-        <f t="shared" si="7"/>
-        <v>12895.819038461537</v>
+        <f t="shared" si="9"/>
+        <v>7369.0394505494496</v>
       </c>
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
@@ -25789,11 +25789,11 @@
         <v>0</v>
       </c>
       <c r="T210" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U210" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -25829,12 +25829,12 @@
         <v>0.20622419686049287</v>
       </c>
       <c r="T211" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>670582.59</v>
       </c>
       <c r="U211" s="65">
-        <f t="shared" si="7"/>
-        <v>12895.819038461537</v>
+        <f t="shared" si="9"/>
+        <v>7369.0394505494496</v>
       </c>
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
@@ -25851,11 +25851,11 @@
       <c r="Q212" s="58"/>
       <c r="R212" s="59"/>
       <c r="T212" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U212" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -25873,11 +25873,11 @@
       <c r="Q213" s="58"/>
       <c r="R213" s="59"/>
       <c r="T213" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U213" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -25910,11 +25910,11 @@
         <v>0</v>
       </c>
       <c r="T214" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U214" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -25947,12 +25947,12 @@
         <v>2.593529470861251E-2</v>
       </c>
       <c r="T215" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>89805.08</v>
       </c>
       <c r="U215" s="65">
-        <f t="shared" si="7"/>
-        <v>1727.0207692307692</v>
+        <f t="shared" si="9"/>
+        <v>986.86901098901103</v>
       </c>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
@@ -25984,12 +25984,12 @@
         <v>2.6644321662604224E-4</v>
       </c>
       <c r="T216" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>7116.9999999999991</v>
       </c>
       <c r="U216" s="65">
-        <f t="shared" si="7"/>
-        <v>136.86538461538458</v>
+        <f t="shared" si="9"/>
+        <v>78.208791208791197</v>
       </c>
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
@@ -26021,12 +26021,12 @@
         <v>1.834159058250202E-2</v>
       </c>
       <c r="T217" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>29438.200000000004</v>
       </c>
       <c r="U217" s="65">
-        <f t="shared" si="7"/>
-        <v>566.11923076923085</v>
+        <f t="shared" si="9"/>
+        <v>323.49670329670334</v>
       </c>
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
@@ -26058,12 +26058,12 @@
         <v>5.6693899934705109E-4</v>
       </c>
       <c r="T218" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2948</v>
       </c>
       <c r="U218" s="65">
-        <f t="shared" si="7"/>
-        <v>56.692307692307693</v>
+        <f t="shared" si="9"/>
+        <v>32.395604395604394</v>
       </c>
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
@@ -26095,12 +26095,12 @@
         <v>1.0050089603984324E-2</v>
       </c>
       <c r="T219" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>44699.46</v>
       </c>
       <c r="U219" s="65">
-        <f t="shared" si="7"/>
-        <v>859.60500000000002</v>
+        <f t="shared" si="9"/>
+        <v>491.20285714285717</v>
       </c>
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
@@ -26132,12 +26132,12 @@
         <v>9.0568052319014622E-4</v>
       </c>
       <c r="T220" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1761.3</v>
       </c>
       <c r="U220" s="65">
-        <f t="shared" si="7"/>
-        <v>33.871153846153845</v>
+        <f t="shared" si="9"/>
+        <v>19.354945054945055</v>
       </c>
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
@@ -26169,12 +26169,12 @@
         <v>3.1290504497189274E-3</v>
       </c>
       <c r="T221" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8343.32</v>
       </c>
       <c r="U221" s="65">
-        <f t="shared" si="7"/>
-        <v>160.44846153846154</v>
+        <f t="shared" si="9"/>
+        <v>91.684835164835164</v>
       </c>
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
@@ -26206,12 +26206,12 @@
         <v>4.8642641621294113E-5</v>
       </c>
       <c r="T222" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>215.95000000000002</v>
       </c>
       <c r="U222" s="65">
-        <f t="shared" si="7"/>
-        <v>4.1528846153846155</v>
+        <f t="shared" si="9"/>
+        <v>2.3730769230769231</v>
       </c>
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
@@ -26243,12 +26243,12 @@
         <v>6.7290044171702711E-6</v>
       </c>
       <c r="T223" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>755.88</v>
       </c>
       <c r="U223" s="65">
-        <f t="shared" si="7"/>
-        <v>14.536153846153846</v>
+        <f t="shared" si="9"/>
+        <v>8.3063736263736256</v>
       </c>
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
@@ -26280,12 +26280,12 @@
         <v>1.2472657985635125E-4</v>
       </c>
       <c r="T224" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>377.78</v>
       </c>
       <c r="U224" s="65">
-        <f t="shared" si="7"/>
-        <v>7.2649999999999997</v>
+        <f t="shared" si="9"/>
+        <v>4.1514285714285712</v>
       </c>
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
@@ -26317,12 +26317,12 @@
         <v>5.8864751023259237E-4</v>
       </c>
       <c r="T225" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>649.97</v>
       </c>
       <c r="U225" s="65">
-        <f t="shared" si="7"/>
-        <v>12.499423076923078</v>
+        <f t="shared" si="9"/>
+        <v>7.1425274725274734</v>
       </c>
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
@@ -26354,12 +26354,12 @@
         <v>2.693865900252082E-4</v>
       </c>
       <c r="T226" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>203.25</v>
       </c>
       <c r="U226" s="65">
-        <f t="shared" si="7"/>
-        <v>3.9086538461538463</v>
+        <f t="shared" si="9"/>
+        <v>2.2335164835164836</v>
       </c>
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
@@ -26391,12 +26391,12 @@
         <v>1.5312515206485841E-3</v>
       </c>
       <c r="T227" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2766.77</v>
       </c>
       <c r="U227" s="65">
-        <f t="shared" si="7"/>
-        <v>53.207115384615385</v>
+        <f t="shared" si="9"/>
+        <v>30.404065934065933</v>
       </c>
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
@@ -26428,12 +26428,12 @@
         <v>8.5683863783106239E-5</v>
       </c>
       <c r="T228" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>515.80999999999995</v>
       </c>
       <c r="U228" s="65">
-        <f t="shared" si="7"/>
-        <v>9.919423076923076</v>
+        <f t="shared" si="9"/>
+        <v>5.6682417582417575</v>
       </c>
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
@@ -26465,12 +26465,12 @@
         <v>0</v>
       </c>
       <c r="T229" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>402</v>
       </c>
       <c r="U229" s="65">
-        <f t="shared" si="7"/>
-        <v>7.7307692307692308</v>
+        <f t="shared" si="9"/>
+        <v>4.4175824175824179</v>
       </c>
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
@@ -26502,12 +26502,12 @@
         <v>1.0990465707150486E-3</v>
       </c>
       <c r="T230" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4666.59</v>
       </c>
       <c r="U230" s="65">
-        <f t="shared" si="7"/>
-        <v>89.742115384615389</v>
+        <f t="shared" si="9"/>
+        <v>51.28120879120879</v>
       </c>
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
@@ -26539,11 +26539,11 @@
         <v>0</v>
       </c>
       <c r="T231" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U231" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -26576,11 +26576,11 @@
         <v>0</v>
       </c>
       <c r="T232" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U232" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -26613,12 +26613,12 @@
         <v>8.2803886118691512E-5</v>
       </c>
       <c r="T233" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>258.27</v>
       </c>
       <c r="U233" s="65">
-        <f t="shared" si="7"/>
-        <v>4.9667307692307689</v>
+        <f t="shared" si="9"/>
+        <v>2.8381318681318679</v>
       </c>
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
@@ -26650,12 +26650,12 @@
         <v>0</v>
       </c>
       <c r="T234" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>179.3</v>
       </c>
       <c r="U234" s="65">
-        <f t="shared" si="7"/>
-        <v>3.4480769230769233</v>
+        <f t="shared" si="9"/>
+        <v>1.9703296703296704</v>
       </c>
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
@@ -26687,12 +26687,12 @@
         <v>3.4272639859888904E-4</v>
       </c>
       <c r="T235" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1884.59</v>
       </c>
       <c r="U235" s="65">
-        <f t="shared" si="7"/>
-        <v>36.242115384615381</v>
+        <f t="shared" si="9"/>
+        <v>20.709780219780217</v>
       </c>
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
@@ -26724,12 +26724,12 @@
         <v>3.3801528041885159E-2</v>
       </c>
       <c r="T236" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>111968.43</v>
       </c>
       <c r="U236" s="65">
-        <f t="shared" si="7"/>
-        <v>2153.2390384615383</v>
+        <f t="shared" si="9"/>
+        <v>1230.4223076923076</v>
       </c>
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
@@ -26761,12 +26761,12 @@
         <v>4.5693562606000495E-3</v>
       </c>
       <c r="T237" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>12624.880000000001</v>
       </c>
       <c r="U237" s="65">
-        <f t="shared" si="7"/>
-        <v>242.78615384615387</v>
+        <f t="shared" si="9"/>
+        <v>138.73494505494506</v>
       </c>
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
@@ -26798,12 +26798,12 @@
         <v>0</v>
       </c>
       <c r="T238" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>128.91999999999999</v>
       </c>
       <c r="U238" s="65">
-        <f t="shared" si="7"/>
-        <v>2.4792307692307691</v>
+        <f t="shared" si="9"/>
+        <v>1.4167032967032966</v>
       </c>
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
@@ -26835,12 +26835,12 @@
         <v>6.2490081397678155E-4</v>
       </c>
       <c r="T239" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2085</v>
       </c>
       <c r="U239" s="65">
-        <f t="shared" si="7"/>
-        <v>40.096153846153847</v>
+        <f t="shared" si="9"/>
+        <v>22.912087912087912</v>
       </c>
     </row>
     <row r="240" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
@@ -26872,11 +26872,11 @@
         <v>0</v>
       </c>
       <c r="T240" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U240" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -26912,12 +26912,12 @@
         <v>0.10237051776645992</v>
       </c>
       <c r="T241" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>323795.74999999988</v>
       </c>
       <c r="U241" s="65">
-        <f t="shared" si="7"/>
-        <v>6226.8413461538439</v>
+        <f t="shared" si="9"/>
+        <v>3558.1950549450535</v>
       </c>
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
@@ -26934,11 +26934,11 @@
       <c r="Q242" s="58"/>
       <c r="R242" s="59"/>
       <c r="T242" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U242" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -26971,11 +26971,11 @@
         <v>0</v>
       </c>
       <c r="T243" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U243" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -27008,12 +27008,12 @@
         <v>5.6134206162186781E-4</v>
       </c>
       <c r="T244" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2136.5500000000002</v>
       </c>
       <c r="U244" s="65">
-        <f t="shared" si="7"/>
-        <v>41.087500000000006</v>
+        <f t="shared" si="9"/>
+        <v>23.478571428571431</v>
       </c>
     </row>
     <row r="245" spans="1:21" x14ac:dyDescent="0.25">
@@ -27045,12 +27045,12 @@
         <v>6.8033585574999724E-4</v>
       </c>
       <c r="T245" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2949.5600000000004</v>
       </c>
       <c r="U245" s="65">
-        <f t="shared" si="7"/>
-        <v>56.722307692307702</v>
+        <f t="shared" si="9"/>
+        <v>32.412747252747259</v>
       </c>
     </row>
     <row r="246" spans="1:21" x14ac:dyDescent="0.25">
@@ -27082,11 +27082,11 @@
         <v>0</v>
       </c>
       <c r="T246" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U246" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -27119,12 +27119,12 @@
         <v>4.3021341820899213E-3</v>
       </c>
       <c r="T247" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>12411.16</v>
       </c>
       <c r="U247" s="65">
-        <f t="shared" si="7"/>
-        <v>238.67615384615385</v>
+        <f t="shared" si="9"/>
+        <v>136.38637362637363</v>
       </c>
     </row>
     <row r="248" spans="1:21" x14ac:dyDescent="0.25">
@@ -27156,12 +27156,12 @@
         <v>8.5211112732532499E-4</v>
       </c>
       <c r="T248" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2430.34</v>
       </c>
       <c r="U248" s="65">
-        <f t="shared" si="7"/>
-        <v>46.737307692307695</v>
+        <f t="shared" si="9"/>
+        <v>26.707032967032969</v>
       </c>
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
@@ -27193,12 +27193,12 @@
         <v>1.7865461444919392E-3</v>
       </c>
       <c r="T249" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10745.58</v>
       </c>
       <c r="U249" s="65">
-        <f t="shared" si="7"/>
-        <v>206.64576923076922</v>
+        <f t="shared" si="9"/>
+        <v>118.0832967032967</v>
       </c>
     </row>
     <row r="250" spans="1:21" x14ac:dyDescent="0.25">
@@ -27230,12 +27230,12 @@
         <v>-3.5411046125350958E-3</v>
       </c>
       <c r="T250" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2206.16</v>
       </c>
       <c r="U250" s="65">
-        <f t="shared" si="7"/>
-        <v>42.426153846153845</v>
+        <f t="shared" si="9"/>
+        <v>24.243516483516483</v>
       </c>
     </row>
     <row r="251" spans="1:21" x14ac:dyDescent="0.25">
@@ -27267,11 +27267,11 @@
         <v>0</v>
       </c>
       <c r="T251" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U251" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -27307,12 +27307,12 @@
         <v>4.6413647587439551E-3</v>
       </c>
       <c r="T252" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>32879.350000000006</v>
       </c>
       <c r="U252" s="65">
-        <f t="shared" si="7"/>
-        <v>632.29519230769245</v>
+        <f t="shared" si="9"/>
+        <v>361.31153846153853</v>
       </c>
     </row>
     <row r="253" spans="1:21" x14ac:dyDescent="0.25">
@@ -27329,11 +27329,11 @@
       <c r="Q253" s="58"/>
       <c r="R253" s="59"/>
       <c r="T253" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U253" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -27366,11 +27366,11 @@
         <v>0</v>
       </c>
       <c r="T254" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U254" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -27403,11 +27403,11 @@
         <v>0</v>
       </c>
       <c r="T255" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U255" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -27440,12 +27440,12 @@
         <v>0</v>
       </c>
       <c r="T256" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>93682.26999999999</v>
       </c>
       <c r="U256" s="65">
-        <f t="shared" si="7"/>
-        <v>1801.5821153846152</v>
+        <f t="shared" si="9"/>
+        <v>1029.4754945054945</v>
       </c>
     </row>
     <row r="257" spans="1:21" x14ac:dyDescent="0.25">
@@ -27477,11 +27477,11 @@
         <v>0</v>
       </c>
       <c r="T257" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U257" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -27514,12 +27514,12 @@
         <v>0</v>
       </c>
       <c r="T258" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>27717.8</v>
       </c>
       <c r="U258" s="65">
-        <f t="shared" si="7"/>
-        <v>533.03461538461534</v>
+        <f t="shared" si="9"/>
+        <v>304.59120879120877</v>
       </c>
     </row>
     <row r="259" spans="1:21" x14ac:dyDescent="0.25">
@@ -27551,11 +27551,11 @@
         <v>0</v>
       </c>
       <c r="T259" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U259" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -27588,11 +27588,11 @@
         <v>0</v>
       </c>
       <c r="T260" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U260" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -27625,12 +27625,12 @@
         <v>3.1479523408616948E-2</v>
       </c>
       <c r="T261" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>104039.19</v>
       </c>
       <c r="U261" s="65">
-        <f t="shared" si="7"/>
-        <v>2000.7536538461538</v>
+        <f t="shared" si="9"/>
+        <v>1143.2878021978022</v>
       </c>
     </row>
     <row r="262" spans="1:21" x14ac:dyDescent="0.25">
@@ -27662,12 +27662,12 @@
         <v>2.4706948008605483E-3</v>
       </c>
       <c r="T262" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8421.77</v>
       </c>
       <c r="U262" s="65">
-        <f t="shared" si="7"/>
-        <v>161.95711538461541</v>
+        <f t="shared" si="9"/>
+        <v>92.546923076923093</v>
       </c>
     </row>
     <row r="263" spans="1:21" x14ac:dyDescent="0.25">
@@ -27702,12 +27702,12 @@
         <v>3.3950218209477502E-2</v>
       </c>
       <c r="T263" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>233861.03000000003</v>
       </c>
       <c r="U263" s="65">
-        <f t="shared" si="7"/>
-        <v>4497.3275000000003</v>
+        <f t="shared" si="9"/>
+        <v>2569.9014285714288</v>
       </c>
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.25">
@@ -27724,11 +27724,11 @@
       <c r="Q264" s="58"/>
       <c r="R264" s="59"/>
       <c r="T264" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U264" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -27761,11 +27761,11 @@
         <v>0</v>
       </c>
       <c r="T265" s="65">
-        <f t="shared" ref="T265:T327" si="8">IFERROR(B265+E265+H265+K265+N265+Q265, "NA")</f>
+        <f t="shared" ref="T265:T327" si="10">IFERROR(B265+E265+H265+K265+N265+Q265, "NA")</f>
         <v>0</v>
       </c>
       <c r="U265" s="65">
-        <f t="shared" ref="U265:U327" si="9">(T265/$V$1)/4</f>
+        <f t="shared" ref="U265:U327" si="11">(T265/$V$1)/7</f>
         <v>0</v>
       </c>
     </row>
@@ -27798,11 +27798,11 @@
         <v>0</v>
       </c>
       <c r="T266" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U266" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27835,11 +27835,11 @@
         <v>0</v>
       </c>
       <c r="T267" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U267" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27872,12 +27872,12 @@
         <v>-6.8838711406340826E-5</v>
       </c>
       <c r="T268" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-196.01</v>
       </c>
       <c r="U268" s="65">
-        <f t="shared" si="9"/>
-        <v>-3.7694230769230765</v>
+        <f t="shared" si="11"/>
+        <v>-2.1539560439560437</v>
       </c>
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.25">
@@ -27909,11 +27909,11 @@
         <v>0</v>
       </c>
       <c r="T269" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U269" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27946,11 +27946,11 @@
         <v>0</v>
       </c>
       <c r="T270" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U270" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -27983,11 +27983,11 @@
         <v>0</v>
       </c>
       <c r="T271" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U271" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28020,11 +28020,11 @@
         <v>0</v>
       </c>
       <c r="T272" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U272" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28057,11 +28057,11 @@
         <v>0</v>
       </c>
       <c r="T273" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U273" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28094,11 +28094,11 @@
         <v>0</v>
       </c>
       <c r="T274" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U274" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28131,11 +28131,11 @@
         <v>0</v>
       </c>
       <c r="T275" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U275" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28168,11 +28168,11 @@
         <v>0</v>
       </c>
       <c r="T276" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U276" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28205,11 +28205,11 @@
         <v>0</v>
       </c>
       <c r="T277" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U277" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28242,12 +28242,12 @@
         <v>-3.1164265476232425E-2</v>
       </c>
       <c r="T278" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-111069.34999999999</v>
       </c>
       <c r="U278" s="65">
-        <f t="shared" si="9"/>
-        <v>-2135.9490384615383</v>
+        <f t="shared" si="11"/>
+        <v>-1220.5423076923075</v>
       </c>
     </row>
     <row r="279" spans="1:21" x14ac:dyDescent="0.25">
@@ -28279,11 +28279,11 @@
         <v>0</v>
       </c>
       <c r="T279" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U279" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28316,11 +28316,11 @@
         <v>0</v>
       </c>
       <c r="T280" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U280" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28353,11 +28353,11 @@
         <v>0</v>
       </c>
       <c r="T281" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U281" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28390,11 +28390,11 @@
         <v>0</v>
       </c>
       <c r="T282" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U282" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28430,12 +28430,12 @@
         <v>-3.1233104187638767E-2</v>
       </c>
       <c r="T283" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-111265.35999999999</v>
       </c>
       <c r="U283" s="65">
-        <f t="shared" si="9"/>
-        <v>-2139.7184615384613</v>
+        <f t="shared" si="11"/>
+        <v>-1222.6962637362635</v>
       </c>
     </row>
     <row r="284" spans="1:21" x14ac:dyDescent="0.25">
@@ -28470,12 +28470,12 @@
         <v>0.10972899654704259</v>
       </c>
       <c r="T284" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>479270.7699999999</v>
       </c>
       <c r="U284" s="65">
-        <f t="shared" si="9"/>
-        <v>9216.7455769230746</v>
+        <f t="shared" si="11"/>
+        <v>5266.7117582417568</v>
       </c>
     </row>
     <row r="285" spans="1:21" x14ac:dyDescent="0.25">
@@ -28492,11 +28492,11 @@
       <c r="Q285" s="58"/>
       <c r="R285" s="59"/>
       <c r="T285" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U285" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28514,11 +28514,11 @@
       <c r="Q286" s="58"/>
       <c r="R286" s="59"/>
       <c r="T286" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U286" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28551,11 +28551,11 @@
         <v>0</v>
       </c>
       <c r="T287" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U287" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28588,11 +28588,11 @@
         <v>0</v>
       </c>
       <c r="T288" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U288" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28625,12 +28625,12 @@
         <v>-4.5282667679476924E-4</v>
       </c>
       <c r="T289" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>13025.39</v>
       </c>
       <c r="U289" s="65">
-        <f t="shared" si="9"/>
-        <v>250.48826923076922</v>
+        <f t="shared" si="11"/>
+        <v>143.13615384615383</v>
       </c>
     </row>
     <row r="290" spans="1:21" x14ac:dyDescent="0.25">
@@ -28662,12 +28662,12 @@
         <v>5.2536208405979189E-2</v>
       </c>
       <c r="T290" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>181695.29</v>
       </c>
       <c r="U290" s="65">
-        <f t="shared" si="9"/>
-        <v>3494.1401923076924</v>
+        <f t="shared" si="11"/>
+        <v>1996.6515384615384</v>
       </c>
     </row>
     <row r="291" spans="1:21" x14ac:dyDescent="0.25">
@@ -28699,11 +28699,11 @@
         <v>0</v>
       </c>
       <c r="T291" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U291" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28736,12 +28736,12 @@
         <v>1.811306707179077E-3</v>
       </c>
       <c r="T292" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7540.71</v>
       </c>
       <c r="U292" s="65">
-        <f t="shared" si="9"/>
-        <v>145.01365384615386</v>
+        <f t="shared" si="11"/>
+        <v>82.864945054945068</v>
       </c>
     </row>
     <row r="293" spans="1:21" x14ac:dyDescent="0.25">
@@ -28773,12 +28773,12 @@
         <v>0</v>
       </c>
       <c r="T293" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>180.10000000000002</v>
       </c>
       <c r="U293" s="65">
-        <f t="shared" si="9"/>
-        <v>3.463461538461539</v>
+        <f t="shared" si="11"/>
+        <v>1.9791208791208794</v>
       </c>
     </row>
     <row r="294" spans="1:21" x14ac:dyDescent="0.25">
@@ -28810,12 +28810,12 @@
         <v>7.3755503462978426E-4</v>
       </c>
       <c r="T294" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>4930.6600000000008</v>
       </c>
       <c r="U294" s="65">
-        <f t="shared" si="9"/>
-        <v>94.820384615384626</v>
+        <f t="shared" si="11"/>
+        <v>54.183076923076932</v>
       </c>
     </row>
     <row r="295" spans="1:21" x14ac:dyDescent="0.25">
@@ -28847,12 +28847,12 @@
         <v>0</v>
       </c>
       <c r="T295" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1542.78</v>
       </c>
       <c r="U295" s="65">
-        <f t="shared" si="9"/>
-        <v>29.668846153846154</v>
+        <f t="shared" si="11"/>
+        <v>16.953626373626374</v>
       </c>
     </row>
     <row r="296" spans="1:21" x14ac:dyDescent="0.25">
@@ -28884,11 +28884,11 @@
         <v>0</v>
       </c>
       <c r="T296" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U296" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28921,12 +28921,12 @@
         <v>0</v>
       </c>
       <c r="T297" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>601.67999999999995</v>
       </c>
       <c r="U297" s="65">
-        <f t="shared" si="9"/>
-        <v>11.57076923076923</v>
+        <f t="shared" si="11"/>
+        <v>6.6118681318681309</v>
       </c>
     </row>
     <row r="298" spans="1:21" x14ac:dyDescent="0.25">
@@ -28958,11 +28958,11 @@
         <v>0</v>
       </c>
       <c r="T298" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U298" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -28995,11 +28995,11 @@
         <v>0</v>
       </c>
       <c r="T299" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U299" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29032,11 +29032,11 @@
         <v>0</v>
       </c>
       <c r="T300" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U300" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29069,11 +29069,11 @@
         <v>0</v>
       </c>
       <c r="T301" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U301" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29106,11 +29106,11 @@
         <v>0</v>
       </c>
       <c r="T302" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U302" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29143,11 +29143,11 @@
         <v>0</v>
       </c>
       <c r="T303" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U303" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29180,11 +29180,11 @@
         <v>0</v>
       </c>
       <c r="T304" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U304" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29217,11 +29217,11 @@
         <v>0</v>
       </c>
       <c r="T305" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U305" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29254,11 +29254,11 @@
         <v>0</v>
       </c>
       <c r="T306" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U306" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29291,11 +29291,11 @@
         <v>0</v>
       </c>
       <c r="T307" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U307" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29328,11 +29328,11 @@
         <v>0</v>
       </c>
       <c r="T308" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U308" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29365,11 +29365,11 @@
         <v>0</v>
       </c>
       <c r="T309" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U309" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29402,11 +29402,11 @@
         <v>0</v>
       </c>
       <c r="T310" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U310" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29439,11 +29439,11 @@
         <v>0</v>
       </c>
       <c r="T311" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U311" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29476,11 +29476,11 @@
         <v>0</v>
       </c>
       <c r="T312" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U312" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29513,11 +29513,11 @@
         <v>0</v>
       </c>
       <c r="T313" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U313" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29553,12 +29553,12 @@
         <v>5.4632243470993276E-2</v>
       </c>
       <c r="T314" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>209516.61000000002</v>
       </c>
       <c r="U314" s="65">
-        <f t="shared" si="9"/>
-        <v>4029.1655769230774</v>
+        <f t="shared" si="11"/>
+        <v>2302.38032967033</v>
       </c>
     </row>
     <row r="315" spans="1:21" x14ac:dyDescent="0.25">
@@ -29575,11 +29575,11 @@
       <c r="Q315" s="58"/>
       <c r="R315" s="59"/>
       <c r="T315" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U315" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29612,11 +29612,11 @@
         <v>0</v>
       </c>
       <c r="T316" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U316" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29649,12 +29649,12 @@
         <v>0</v>
       </c>
       <c r="T317" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1000</v>
       </c>
       <c r="U317" s="65">
-        <f t="shared" si="9"/>
-        <v>19.23076923076923</v>
+        <f t="shared" si="11"/>
+        <v>10.989010989010989</v>
       </c>
     </row>
     <row r="318" spans="1:21" x14ac:dyDescent="0.25">
@@ -29686,12 +29686,12 @@
         <v>0</v>
       </c>
       <c r="T318" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>25000</v>
       </c>
       <c r="U318" s="65">
-        <f t="shared" si="9"/>
-        <v>480.76923076923077</v>
+        <f t="shared" si="11"/>
+        <v>274.72527472527474</v>
       </c>
     </row>
     <row r="319" spans="1:21" x14ac:dyDescent="0.25">
@@ -29723,12 +29723,12 @@
         <v>0</v>
       </c>
       <c r="T319" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3551.35</v>
       </c>
       <c r="U319" s="65">
-        <f t="shared" si="9"/>
-        <v>68.295192307692304</v>
+        <f t="shared" si="11"/>
+        <v>39.025824175824177</v>
       </c>
     </row>
     <row r="320" spans="1:21" x14ac:dyDescent="0.25">
@@ -29760,11 +29760,11 @@
         <v>0</v>
       </c>
       <c r="T320" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U320" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -29797,12 +29797,12 @@
         <v>0</v>
       </c>
       <c r="T321" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>31.9</v>
       </c>
       <c r="U321" s="65">
-        <f t="shared" si="9"/>
-        <v>0.61346153846153839</v>
+        <f t="shared" si="11"/>
+        <v>0.35054945054945053</v>
       </c>
     </row>
     <row r="322" spans="1:21" x14ac:dyDescent="0.25">
@@ -29834,12 +29834,12 @@
         <v>1.0368825245246627E-2</v>
       </c>
       <c r="T322" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>37319.5</v>
       </c>
       <c r="U322" s="65">
-        <f t="shared" si="9"/>
-        <v>717.68269230769226</v>
+        <f t="shared" si="11"/>
+        <v>410.10439560439556</v>
       </c>
     </row>
     <row r="323" spans="1:21" x14ac:dyDescent="0.25">
@@ -29871,12 +29871,12 @@
         <v>0</v>
       </c>
       <c r="T323" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>428.3</v>
       </c>
       <c r="U323" s="65">
-        <f t="shared" si="9"/>
-        <v>8.236538461538462</v>
+        <f t="shared" si="11"/>
+        <v>4.7065934065934067</v>
       </c>
     </row>
     <row r="324" spans="1:21" x14ac:dyDescent="0.25">
@@ -29911,12 +29911,12 @@
         <v>1.0368825245246627E-2</v>
       </c>
       <c r="T324" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>67331.05</v>
       </c>
       <c r="U324" s="65">
-        <f t="shared" si="9"/>
-        <v>1294.8278846153846</v>
+        <f t="shared" si="11"/>
+        <v>739.9016483516483</v>
       </c>
     </row>
     <row r="325" spans="1:21" x14ac:dyDescent="0.25">
@@ -29951,12 +29951,12 @@
         <v>6.500106871623991E-2</v>
       </c>
       <c r="T325" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>276847.66000000003</v>
       </c>
       <c r="U325" s="65">
-        <f t="shared" si="9"/>
-        <v>5323.9934615384618</v>
+        <f t="shared" si="11"/>
+        <v>3042.2819780219784</v>
       </c>
     </row>
     <row r="326" spans="1:21" x14ac:dyDescent="0.25">
@@ -29991,12 +29991,12 @@
         <v>0.31665596229685411</v>
       </c>
       <c r="T326" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1014674.31</v>
       </c>
       <c r="U326" s="65">
-        <f t="shared" si="9"/>
-        <v>19512.967500000002</v>
+        <f t="shared" si="11"/>
+        <v>11150.267142857145</v>
       </c>
     </row>
     <row r="327" spans="1:21" x14ac:dyDescent="0.25">
@@ -30019,12 +30019,12 @@
       </c>
       <c r="R327" s="75"/>
       <c r="T327" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3457440.69</v>
       </c>
       <c r="U327" s="65">
-        <f t="shared" si="9"/>
-        <v>66489.244038461533</v>
+        <f t="shared" si="11"/>
+        <v>37993.853736263736</v>
       </c>
     </row>
     <row r="330" spans="1:21" x14ac:dyDescent="0.25">
